--- a/DATA/EVALUACIONES/Exp01/predicciones.xlsx
+++ b/DATA/EVALUACIONES/Exp01/predicciones.xlsx
@@ -445,7 +445,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.469518542289734</v>
+        <v>0.04593554139137268</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.451445579528809</v>
+        <v>0.02912991680204868</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.573496341705322</v>
+        <v>0.02723921276628971</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.626175880432129</v>
+        <v>0.023912712931633</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.691092252731323</v>
+        <v>0.02319801226258278</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>17</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.627071142196655</v>
+        <v>0.01824825070798397</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.610258340835571</v>
+        <v>0.008354236371815205</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.63685417175293</v>
+        <v>0.005180965177714825</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.616144418716431</v>
+        <v>0.004270600154995918</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>21</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.596101641654968</v>
+        <v>0.005375348962843418</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.554669141769409</v>
+        <v>0.01211670320481062</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.413223266601562</v>
+        <v>0.06854584813117981</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>24</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.245548009872437</v>
+        <v>0.2649800777435303</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>25</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.198376655578613</v>
+        <v>0.3345495760440826</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>26</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.169687032699585</v>
+        <v>0.1738482415676117</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>27</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.232953071594238</v>
+        <v>0.09606752544641495</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>28</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.198029518127441</v>
+        <v>0.04029504954814911</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>29</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.205901145935059</v>
+        <v>0.01411005668342113</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.191545724868774</v>
+        <v>0.004366395063698292</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>31</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.157598257064819</v>
+        <v>0.002379999961704016</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>32</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.153421640396118</v>
+        <v>0.001358728972263634</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>33</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.14145565032959</v>
+        <v>0.001253130030818284</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>34</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.136907458305359</v>
+        <v>0.001781513215973973</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>35</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.020574808120728</v>
+        <v>0.004068574868142605</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>36</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.9160462021827698</v>
+        <v>0.02376882918179035</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>37</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.8922659754753113</v>
+        <v>0.08357137441635132</v>
       </c>
     </row>
     <row r="28">
@@ -653,7 +653,7 @@
         <v>38</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.9221361875534058</v>
+        <v>0.03843735530972481</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.9318068027496338</v>
+        <v>0.03378285095095634</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>40</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.9498201012611389</v>
+        <v>0.01819770224392414</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>41</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.9525415301322937</v>
+        <v>0.007404145784676075</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>42</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.9792982935905457</v>
+        <v>0.003692363388836384</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>43</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.048794865608215</v>
+        <v>0.001620681956410408</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>44</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.036792397499084</v>
+        <v>0.001240215846337378</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>45</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.078793048858643</v>
+        <v>0.0009960116585716605</v>
       </c>
     </row>
     <row r="36">
@@ -717,7 +717,7 @@
         <v>46</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.043745040893555</v>
+        <v>0.0009792367927730083</v>
       </c>
     </row>
     <row r="37">
@@ -725,7 +725,7 @@
         <v>47</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.9794569611549377</v>
+        <v>0.001347069512121379</v>
       </c>
     </row>
     <row r="38">
@@ -733,7 +733,7 @@
         <v>48</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.9339180588722229</v>
+        <v>0.0036396908108145</v>
       </c>
     </row>
     <row r="39">
@@ -741,7 +741,7 @@
         <v>49</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.9309132695198059</v>
+        <v>0.01347522065043449</v>
       </c>
     </row>
     <row r="40">
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.021449327468872</v>
+        <v>0.02124750800430775</v>
       </c>
     </row>
     <row r="41">
@@ -757,7 +757,7 @@
         <v>51</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.111137986183167</v>
+        <v>0.02368221990764141</v>
       </c>
     </row>
     <row r="42">
@@ -765,7 +765,7 @@
         <v>52</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.09930682182312</v>
+        <v>0.02491008676588535</v>
       </c>
     </row>
     <row r="43">
@@ -773,7 +773,7 @@
         <v>53</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.126628160476685</v>
+        <v>0.02399147860705853</v>
       </c>
     </row>
     <row r="44">
@@ -781,7 +781,7 @@
         <v>54</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.109073162078857</v>
+        <v>0.01224401872605085</v>
       </c>
     </row>
     <row r="45">
@@ -789,7 +789,7 @@
         <v>55</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.121824502944946</v>
+        <v>0.005913697183132172</v>
       </c>
     </row>
     <row r="46">
@@ -797,7 +797,7 @@
         <v>56</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.13508665561676</v>
+        <v>0.003565440187230706</v>
       </c>
     </row>
     <row r="47">
@@ -805,7 +805,7 @@
         <v>57</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.143489241600037</v>
+        <v>0.003733055666089058</v>
       </c>
     </row>
     <row r="48">
@@ -813,7 +813,7 @@
         <v>58</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.14979350566864</v>
+        <v>0.005590613000094891</v>
       </c>
     </row>
     <row r="49">
@@ -821,7 +821,7 @@
         <v>59</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.02574348449707</v>
+        <v>0.02457905746996403</v>
       </c>
     </row>
     <row r="50">
@@ -829,7 +829,7 @@
         <v>60</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.9407281279563904</v>
+        <v>0.1557310968637466</v>
       </c>
     </row>
     <row r="51">
@@ -837,7 +837,7 @@
         <v>61</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.8698243498802185</v>
+        <v>0.1420497447252274</v>
       </c>
     </row>
     <row r="52">
@@ -845,7 +845,7 @@
         <v>62</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.8974317908287048</v>
+        <v>0.1135742515325546</v>
       </c>
     </row>
     <row r="53">
@@ -853,7 +853,7 @@
         <v>63</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.938884437084198</v>
+        <v>0.1108372732996941</v>
       </c>
     </row>
     <row r="54">
@@ -861,7 +861,7 @@
         <v>64</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.019113183021545</v>
+        <v>0.09441749006509781</v>
       </c>
     </row>
     <row r="55">
@@ -869,7 +869,7 @@
         <v>65</v>
       </c>
       <c r="B55" t="n">
-        <v>-1.034691095352173</v>
+        <v>0.09989631921052933</v>
       </c>
     </row>
     <row r="56">
@@ -877,7 +877,7 @@
         <v>66</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.071650505065918</v>
+        <v>0.09400882571935654</v>
       </c>
     </row>
     <row r="57">
@@ -885,7 +885,7 @@
         <v>67</v>
       </c>
       <c r="B57" t="n">
-        <v>-1.116231322288513</v>
+        <v>0.05245587229728699</v>
       </c>
     </row>
     <row r="58">
@@ -893,7 +893,7 @@
         <v>68</v>
       </c>
       <c r="B58" t="n">
-        <v>-1.167728781700134</v>
+        <v>0.01745335571467876</v>
       </c>
     </row>
     <row r="59">
@@ -901,7 +901,7 @@
         <v>69</v>
       </c>
       <c r="B59" t="n">
-        <v>-1.163821935653687</v>
+        <v>0.01308885682374239</v>
       </c>
     </row>
     <row r="60">
@@ -909,7 +909,7 @@
         <v>70</v>
       </c>
       <c r="B60" t="n">
-        <v>-1.176718235015869</v>
+        <v>0.02495341375470161</v>
       </c>
     </row>
     <row r="61">
@@ -917,7 +917,7 @@
         <v>71</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.161721706390381</v>
+        <v>0.05651307478547096</v>
       </c>
     </row>
     <row r="62">
@@ -925,7 +925,7 @@
         <v>72</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.152423739433289</v>
+        <v>0.1261675208806992</v>
       </c>
     </row>
     <row r="63">
@@ -933,7 +933,7 @@
         <v>73</v>
       </c>
       <c r="B63" t="n">
-        <v>-1.191501498222351</v>
+        <v>0.06992020457983017</v>
       </c>
     </row>
     <row r="64">
@@ -941,7 +941,7 @@
         <v>74</v>
       </c>
       <c r="B64" t="n">
-        <v>-1.284687757492065</v>
+        <v>0.02649426460266113</v>
       </c>
     </row>
     <row r="65">
@@ -949,7 +949,7 @@
         <v>75</v>
       </c>
       <c r="B65" t="n">
-        <v>-1.333970308303833</v>
+        <v>0.01508629694581032</v>
       </c>
     </row>
     <row r="66">
@@ -957,7 +957,7 @@
         <v>76</v>
       </c>
       <c r="B66" t="n">
-        <v>-1.319688677787781</v>
+        <v>0.006853778846561909</v>
       </c>
     </row>
     <row r="67">
@@ -965,7 +965,7 @@
         <v>77</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.307380437850952</v>
+        <v>0.003913952969014645</v>
       </c>
     </row>
     <row r="68">
@@ -973,7 +973,7 @@
         <v>78</v>
       </c>
       <c r="B68" t="n">
-        <v>-1.318714380264282</v>
+        <v>0.002292668679729104</v>
       </c>
     </row>
     <row r="69">
@@ -981,7 +981,7 @@
         <v>79</v>
       </c>
       <c r="B69" t="n">
-        <v>-1.344363212585449</v>
+        <v>0.001876073190942407</v>
       </c>
     </row>
     <row r="70">
@@ -989,7 +989,7 @@
         <v>80</v>
       </c>
       <c r="B70" t="n">
-        <v>-1.365923404693604</v>
+        <v>0.001702488632872701</v>
       </c>
     </row>
     <row r="71">
@@ -997,7 +997,7 @@
         <v>81</v>
       </c>
       <c r="B71" t="n">
-        <v>-1.382200241088867</v>
+        <v>0.001583588658832014</v>
       </c>
     </row>
     <row r="72">
@@ -1005,7 +1005,7 @@
         <v>82</v>
       </c>
       <c r="B72" t="n">
-        <v>-1.360807180404663</v>
+        <v>0.001931131700985134</v>
       </c>
     </row>
     <row r="73">
@@ -1013,7 +1013,7 @@
         <v>83</v>
       </c>
       <c r="B73" t="n">
-        <v>-1.314359307289124</v>
+        <v>0.003713259706273675</v>
       </c>
     </row>
     <row r="74">
@@ -1021,7 +1021,7 @@
         <v>84</v>
       </c>
       <c r="B74" t="n">
-        <v>-1.246764183044434</v>
+        <v>0.008592892438173294</v>
       </c>
     </row>
     <row r="75">
@@ -1029,7 +1029,7 @@
         <v>85</v>
       </c>
       <c r="B75" t="n">
-        <v>-1.208641886711121</v>
+        <v>0.01201532687991858</v>
       </c>
     </row>
     <row r="76">
@@ -1037,7 +1037,7 @@
         <v>86</v>
       </c>
       <c r="B76" t="n">
-        <v>-1.273940563201904</v>
+        <v>0.02001539804041386</v>
       </c>
     </row>
     <row r="77">
@@ -1045,7 +1045,7 @@
         <v>87</v>
       </c>
       <c r="B77" t="n">
-        <v>-1.272417545318604</v>
+        <v>0.03331121802330017</v>
       </c>
     </row>
     <row r="78">
@@ -1053,7 +1053,7 @@
         <v>88</v>
       </c>
       <c r="B78" t="n">
-        <v>-1.272984266281128</v>
+        <v>0.03981519863009453</v>
       </c>
     </row>
     <row r="79">
@@ -1061,7 +1061,7 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>-1.269466876983643</v>
+        <v>0.02464169636368752</v>
       </c>
     </row>
     <row r="80">
@@ -1069,7 +1069,7 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>-1.274198055267334</v>
+        <v>0.01559001300483942</v>
       </c>
     </row>
     <row r="81">
@@ -1077,7 +1077,7 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>-1.281218290328979</v>
+        <v>0.005631938576698303</v>
       </c>
     </row>
     <row r="82">
@@ -1085,7 +1085,7 @@
         <v>92</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.280308842658997</v>
+        <v>0.003659020643681288</v>
       </c>
     </row>
     <row r="83">
@@ -1093,7 +1093,7 @@
         <v>93</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.297822237014771</v>
+        <v>0.002390304813161492</v>
       </c>
     </row>
     <row r="84">
@@ -1101,7 +1101,7 @@
         <v>94</v>
       </c>
       <c r="B84" t="n">
-        <v>-1.26654314994812</v>
+        <v>0.002525858115404844</v>
       </c>
     </row>
     <row r="85">
@@ -1109,7 +1109,7 @@
         <v>95</v>
       </c>
       <c r="B85" t="n">
-        <v>-1.183878898620605</v>
+        <v>0.002560153137892485</v>
       </c>
     </row>
     <row r="86">
@@ -1117,7 +1117,7 @@
         <v>96</v>
       </c>
       <c r="B86" t="n">
-        <v>-1.09605860710144</v>
+        <v>0.001979672117158771</v>
       </c>
     </row>
     <row r="87">
@@ -1125,7 +1125,7 @@
         <v>97</v>
       </c>
       <c r="B87" t="n">
-        <v>-1.07784640789032</v>
+        <v>0.001589320483617485</v>
       </c>
     </row>
     <row r="88">
@@ -1133,7 +1133,7 @@
         <v>98</v>
       </c>
       <c r="B88" t="n">
-        <v>-1.059455752372742</v>
+        <v>0.001222058665007353</v>
       </c>
     </row>
     <row r="89">
@@ -1141,7 +1141,7 @@
         <v>99</v>
       </c>
       <c r="B89" t="n">
-        <v>-1.108198404312134</v>
+        <v>0.001188809284940362</v>
       </c>
     </row>
     <row r="90">
@@ -1149,7 +1149,7 @@
         <v>100</v>
       </c>
       <c r="B90" t="n">
-        <v>-1.075005173683167</v>
+        <v>0.001115997205488384</v>
       </c>
     </row>
     <row r="91">
@@ -1157,7 +1157,7 @@
         <v>101</v>
       </c>
       <c r="B91" t="n">
-        <v>-1.035561680793762</v>
+        <v>0.0009806468151509762</v>
       </c>
     </row>
     <row r="92">
@@ -1165,7 +1165,7 @@
         <v>102</v>
       </c>
       <c r="B92" t="n">
-        <v>-1.020239591598511</v>
+        <v>0.001006039557978511</v>
       </c>
     </row>
     <row r="93">
@@ -1173,7 +1173,7 @@
         <v>103</v>
       </c>
       <c r="B93" t="n">
-        <v>-1.022126793861389</v>
+        <v>0.001031213672831655</v>
       </c>
     </row>
     <row r="94">
@@ -1181,7 +1181,7 @@
         <v>104</v>
       </c>
       <c r="B94" t="n">
-        <v>-1.036999464035034</v>
+        <v>0.0009860665304586291</v>
       </c>
     </row>
     <row r="95">
@@ -1189,7 +1189,7 @@
         <v>105</v>
       </c>
       <c r="B95" t="n">
-        <v>-1.081790804862976</v>
+        <v>0.001401552814058959</v>
       </c>
     </row>
     <row r="96">
@@ -1197,7 +1197,7 @@
         <v>106</v>
       </c>
       <c r="B96" t="n">
-        <v>-1.112053036689758</v>
+        <v>0.002379864454269409</v>
       </c>
     </row>
     <row r="97">
@@ -1205,7 +1205,7 @@
         <v>107</v>
       </c>
       <c r="B97" t="n">
-        <v>-1.113222718238831</v>
+        <v>0.00671222573146224</v>
       </c>
     </row>
     <row r="98">
@@ -1213,7 +1213,7 @@
         <v>108</v>
       </c>
       <c r="B98" t="n">
-        <v>-1.10950493812561</v>
+        <v>0.02059014327824116</v>
       </c>
     </row>
     <row r="99">
@@ -1221,7 +1221,7 @@
         <v>109</v>
       </c>
       <c r="B99" t="n">
-        <v>-1.091507911682129</v>
+        <v>0.02044622600078583</v>
       </c>
     </row>
     <row r="100">
@@ -1229,7 +1229,7 @@
         <v>110</v>
       </c>
       <c r="B100" t="n">
-        <v>-1.234022736549377</v>
+        <v>0.01950287446379662</v>
       </c>
     </row>
     <row r="101">
@@ -1237,7 +1237,7 @@
         <v>111</v>
       </c>
       <c r="B101" t="n">
-        <v>-1.339268207550049</v>
+        <v>0.02225132286548615</v>
       </c>
     </row>
     <row r="102">
@@ -1245,7 +1245,7 @@
         <v>112</v>
       </c>
       <c r="B102" t="n">
-        <v>-1.400074005126953</v>
+        <v>0.0216647032648325</v>
       </c>
     </row>
     <row r="103">
@@ -1253,7 +1253,7 @@
         <v>113</v>
       </c>
       <c r="B103" t="n">
-        <v>-1.445130109786987</v>
+        <v>0.01967473141849041</v>
       </c>
     </row>
     <row r="104">
@@ -1261,7 +1261,7 @@
         <v>114</v>
       </c>
       <c r="B104" t="n">
-        <v>-1.39568305015564</v>
+        <v>0.009771198034286499</v>
       </c>
     </row>
     <row r="105">
@@ -1269,7 +1269,7 @@
         <v>115</v>
       </c>
       <c r="B105" t="n">
-        <v>-1.330682754516602</v>
+        <v>0.005311957560479641</v>
       </c>
     </row>
     <row r="106">
@@ -1277,7 +1277,7 @@
         <v>116</v>
       </c>
       <c r="B106" t="n">
-        <v>-1.295564651489258</v>
+        <v>0.004247070290148258</v>
       </c>
     </row>
     <row r="107">
@@ -1285,7 +1285,7 @@
         <v>117</v>
       </c>
       <c r="B107" t="n">
-        <v>-1.278848648071289</v>
+        <v>0.00590816093608737</v>
       </c>
     </row>
     <row r="108">
@@ -1293,7 +1293,7 @@
         <v>118</v>
       </c>
       <c r="B108" t="n">
-        <v>-1.216636180877686</v>
+        <v>0.01801323890686035</v>
       </c>
     </row>
     <row r="109">
@@ -1301,7 +1301,7 @@
         <v>119</v>
       </c>
       <c r="B109" t="n">
-        <v>-1.092812418937683</v>
+        <v>0.109422855079174</v>
       </c>
     </row>
     <row r="110">
@@ -1309,7 +1309,7 @@
         <v>120</v>
       </c>
       <c r="B110" t="n">
-        <v>-0.9504768252372742</v>
+        <v>0.3145425915718079</v>
       </c>
     </row>
     <row r="111">
@@ -1317,7 +1317,7 @@
         <v>121</v>
       </c>
       <c r="B111" t="n">
-        <v>-0.9164442420005798</v>
+        <v>0.3522688150405884</v>
       </c>
     </row>
     <row r="112">
@@ -1325,7 +1325,7 @@
         <v>122</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.9414170384407043</v>
+        <v>0.4766989648342133</v>
       </c>
     </row>
     <row r="113">
@@ -1333,7 +1333,7 @@
         <v>123</v>
       </c>
       <c r="B113" t="n">
-        <v>-0.8595914840698242</v>
+        <v>0.5286740064620972</v>
       </c>
     </row>
     <row r="114">
@@ -1341,7 +1341,7 @@
         <v>124</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.7803887724876404</v>
+        <v>0.5940499305725098</v>
       </c>
     </row>
     <row r="115">
@@ -1349,7 +1349,7 @@
         <v>125</v>
       </c>
       <c r="B115" t="n">
-        <v>-0.65618497133255</v>
+        <v>0.6478945016860962</v>
       </c>
     </row>
     <row r="116">
@@ -1357,7 +1357,7 @@
         <v>126</v>
       </c>
       <c r="B116" t="n">
-        <v>-0.6034530997276306</v>
+        <v>0.679085373878479</v>
       </c>
     </row>
     <row r="117">
@@ -1365,7 +1365,7 @@
         <v>127</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.6560012698173523</v>
+        <v>0.6391006708145142</v>
       </c>
     </row>
     <row r="118">
@@ -1373,7 +1373,7 @@
         <v>128</v>
       </c>
       <c r="B118" t="n">
-        <v>-0.7368691563606262</v>
+        <v>0.6029065251350403</v>
       </c>
     </row>
     <row r="119">
@@ -1381,7 +1381,7 @@
         <v>129</v>
       </c>
       <c r="B119" t="n">
-        <v>-0.7795866131782532</v>
+        <v>0.5726328492164612</v>
       </c>
     </row>
     <row r="120">
@@ -1389,7 +1389,7 @@
         <v>130</v>
       </c>
       <c r="B120" t="n">
-        <v>-0.8244596123695374</v>
+        <v>0.5454257130622864</v>
       </c>
     </row>
     <row r="121">
@@ -1397,7 +1397,7 @@
         <v>131</v>
       </c>
       <c r="B121" t="n">
-        <v>-0.8439019322395325</v>
+        <v>0.5484349131584167</v>
       </c>
     </row>
     <row r="122">
@@ -1405,7 +1405,7 @@
         <v>132</v>
       </c>
       <c r="B122" t="n">
-        <v>-0.8512356877326965</v>
+        <v>0.519856333732605</v>
       </c>
     </row>
     <row r="123">
@@ -1413,7 +1413,7 @@
         <v>133</v>
       </c>
       <c r="B123" t="n">
-        <v>-0.8425196409225464</v>
+        <v>0.4616551101207733</v>
       </c>
     </row>
     <row r="124">
@@ -1421,7 +1421,7 @@
         <v>134</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.8725822567939758</v>
+        <v>0.3319942057132721</v>
       </c>
     </row>
     <row r="125">
@@ -1429,7 +1429,7 @@
         <v>135</v>
       </c>
       <c r="B125" t="n">
-        <v>-0.9103749394416809</v>
+        <v>0.2614772915840149</v>
       </c>
     </row>
     <row r="126">
@@ -1437,7 +1437,7 @@
         <v>136</v>
       </c>
       <c r="B126" t="n">
-        <v>-0.8549638390541077</v>
+        <v>0.2327763587236404</v>
       </c>
     </row>
     <row r="127">
@@ -1445,7 +1445,7 @@
         <v>137</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.7975122332572937</v>
+        <v>0.1760090440511703</v>
       </c>
     </row>
     <row r="128">
@@ -1453,7 +1453,7 @@
         <v>138</v>
       </c>
       <c r="B128" t="n">
-        <v>-0.7119995951652527</v>
+        <v>0.1701207011938095</v>
       </c>
     </row>
     <row r="129">
@@ -1461,7 +1461,7 @@
         <v>139</v>
       </c>
       <c r="B129" t="n">
-        <v>-0.6787230372428894</v>
+        <v>0.1240960210561752</v>
       </c>
     </row>
     <row r="130">
@@ -1469,7 +1469,7 @@
         <v>140</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.7036076784133911</v>
+        <v>0.08983072638511658</v>
       </c>
     </row>
     <row r="131">
@@ -1477,7 +1477,7 @@
         <v>141</v>
       </c>
       <c r="B131" t="n">
-        <v>-0.7813231945037842</v>
+        <v>0.04884935170412064</v>
       </c>
     </row>
     <row r="132">
@@ -1485,7 +1485,7 @@
         <v>142</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.7975606322288513</v>
+        <v>0.04132611304521561</v>
       </c>
     </row>
     <row r="133">
@@ -1493,7 +1493,7 @@
         <v>143</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.7564658522605896</v>
+        <v>0.04333212226629257</v>
       </c>
     </row>
     <row r="134">
@@ -1501,7 +1501,7 @@
         <v>144</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.8191671967506409</v>
+        <v>0.03770013153553009</v>
       </c>
     </row>
     <row r="135">
@@ -1509,7 +1509,7 @@
         <v>145</v>
       </c>
       <c r="B135" t="n">
-        <v>-0.8913161158561707</v>
+        <v>0.01672692783176899</v>
       </c>
     </row>
     <row r="136">
@@ -1517,7 +1517,7 @@
         <v>146</v>
       </c>
       <c r="B136" t="n">
-        <v>-0.9944337010383606</v>
+        <v>0.0133839612826705</v>
       </c>
     </row>
     <row r="137">
@@ -1525,7 +1525,7 @@
         <v>147</v>
       </c>
       <c r="B137" t="n">
-        <v>-1.095909118652344</v>
+        <v>0.01224534399807453</v>
       </c>
     </row>
     <row r="138">
@@ -1533,7 +1533,7 @@
         <v>148</v>
       </c>
       <c r="B138" t="n">
-        <v>-1.228622674942017</v>
+        <v>0.01648622751235962</v>
       </c>
     </row>
     <row r="139">
@@ -1541,7 +1541,7 @@
         <v>149</v>
       </c>
       <c r="B139" t="n">
-        <v>-1.207762479782104</v>
+        <v>0.01822703145444393</v>
       </c>
     </row>
     <row r="140">
@@ -1549,7 +1549,7 @@
         <v>150</v>
       </c>
       <c r="B140" t="n">
-        <v>-1.201092958450317</v>
+        <v>0.01677214168012142</v>
       </c>
     </row>
     <row r="141">
@@ -1557,7 +1557,7 @@
         <v>151</v>
       </c>
       <c r="B141" t="n">
-        <v>-1.16754412651062</v>
+        <v>0.01600874774158001</v>
       </c>
     </row>
     <row r="142">
@@ -1565,7 +1565,7 @@
         <v>152</v>
       </c>
       <c r="B142" t="n">
-        <v>-1.085492730140686</v>
+        <v>0.01461647916585207</v>
       </c>
     </row>
     <row r="143">
@@ -1573,7 +1573,7 @@
         <v>153</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.9786397218704224</v>
+        <v>0.01244276575744152</v>
       </c>
     </row>
     <row r="144">
@@ -1581,7 +1581,7 @@
         <v>154</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.7787932753562927</v>
+        <v>0.01198774483054876</v>
       </c>
     </row>
     <row r="145">
@@ -1589,7 +1589,7 @@
         <v>155</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.457123190164566</v>
+        <v>0.01875140145421028</v>
       </c>
     </row>
     <row r="146">
@@ -1597,7 +1597,7 @@
         <v>156</v>
       </c>
       <c r="B146" t="n">
-        <v>-0.2169602662324905</v>
+        <v>0.1187594383955002</v>
       </c>
     </row>
     <row r="147">
@@ -1605,7 +1605,7 @@
         <v>157</v>
       </c>
       <c r="B147" t="n">
-        <v>-0.01698813773691654</v>
+        <v>0.1337929964065552</v>
       </c>
     </row>
     <row r="148">
@@ -1613,7 +1613,7 @@
         <v>158</v>
       </c>
       <c r="B148" t="n">
-        <v>-0.04059256240725517</v>
+        <v>0.01190123986452818</v>
       </c>
     </row>
     <row r="149">
@@ -1621,7 +1621,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="n">
-        <v>-0.04588564485311508</v>
+        <v>0.00290300790220499</v>
       </c>
     </row>
     <row r="150">
@@ -1629,7 +1629,7 @@
         <v>160</v>
       </c>
       <c r="B150" t="n">
-        <v>0.01935346238315105</v>
+        <v>0.002104883315041661</v>
       </c>
     </row>
     <row r="151">
@@ -1637,7 +1637,7 @@
         <v>161</v>
       </c>
       <c r="B151" t="n">
-        <v>-0.04697999358177185</v>
+        <v>0.001689497614279389</v>
       </c>
     </row>
     <row r="152">
@@ -1645,7 +1645,7 @@
         <v>162</v>
       </c>
       <c r="B152" t="n">
-        <v>-0.1515787690877914</v>
+        <v>0.001498096971772611</v>
       </c>
     </row>
     <row r="153">
@@ -1653,7 +1653,7 @@
         <v>163</v>
       </c>
       <c r="B153" t="n">
-        <v>-0.2393627911806107</v>
+        <v>0.001899444381706417</v>
       </c>
     </row>
     <row r="154">
@@ -1661,7 +1661,7 @@
         <v>164</v>
       </c>
       <c r="B154" t="n">
-        <v>-0.3932479619979858</v>
+        <v>0.00155007722787559</v>
       </c>
     </row>
     <row r="155">
@@ -1669,7 +1669,7 @@
         <v>165</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.4984619915485382</v>
+        <v>0.001356840948574245</v>
       </c>
     </row>
     <row r="156">
@@ -1677,7 +1677,7 @@
         <v>166</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.4596050083637238</v>
+        <v>0.001906823250465095</v>
       </c>
     </row>
     <row r="157">
@@ -1685,7 +1685,7 @@
         <v>167</v>
       </c>
       <c r="B157" t="n">
-        <v>-0.2939306497573853</v>
+        <v>0.003714230377227068</v>
       </c>
     </row>
     <row r="158">
@@ -1693,7 +1693,7 @@
         <v>168</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.2641458213329315</v>
+        <v>0.003935495391488075</v>
       </c>
     </row>
     <row r="159">
@@ -1701,7 +1701,7 @@
         <v>169</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.0725175216794014</v>
+        <v>0.006435782182961702</v>
       </c>
     </row>
     <row r="160">
@@ -1709,7 +1709,7 @@
         <v>170</v>
       </c>
       <c r="B160" t="n">
-        <v>-0.1590724736452103</v>
+        <v>0.003463581204414368</v>
       </c>
     </row>
     <row r="161">
@@ -1717,7 +1717,7 @@
         <v>171</v>
       </c>
       <c r="B161" t="n">
-        <v>-0.1064207479357719</v>
+        <v>0.004754597321152687</v>
       </c>
     </row>
     <row r="162">
@@ -1725,7 +1725,7 @@
         <v>172</v>
       </c>
       <c r="B162" t="n">
-        <v>-0.1889969110488892</v>
+        <v>0.003930142149329185</v>
       </c>
     </row>
     <row r="163">
@@ -1733,7 +1733,7 @@
         <v>173</v>
       </c>
       <c r="B163" t="n">
-        <v>-0.1647220999002457</v>
+        <v>0.003084323834627867</v>
       </c>
     </row>
     <row r="164">
@@ -1741,7 +1741,7 @@
         <v>174</v>
       </c>
       <c r="B164" t="n">
-        <v>-0.193106472492218</v>
+        <v>0.0032071303576231</v>
       </c>
     </row>
     <row r="165">
@@ -1749,7 +1749,7 @@
         <v>175</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.2959427535533905</v>
+        <v>0.003576630027964711</v>
       </c>
     </row>
     <row r="166">
@@ -1757,7 +1757,7 @@
         <v>176</v>
       </c>
       <c r="B166" t="n">
-        <v>-0.4540696144104004</v>
+        <v>0.002758306451141834</v>
       </c>
     </row>
     <row r="167">
@@ -1765,7 +1765,7 @@
         <v>177</v>
       </c>
       <c r="B167" t="n">
-        <v>-0.6629197597503662</v>
+        <v>0.001675902050919831</v>
       </c>
     </row>
     <row r="168">
@@ -1773,7 +1773,7 @@
         <v>178</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.7475006580352783</v>
+        <v>0.001261186320334673</v>
       </c>
     </row>
     <row r="169">
@@ -1781,7 +1781,7 @@
         <v>179</v>
       </c>
       <c r="B169" t="n">
-        <v>-0.7655784487724304</v>
+        <v>0.001053647021763027</v>
       </c>
     </row>
     <row r="170">
@@ -1789,7 +1789,7 @@
         <v>180</v>
       </c>
       <c r="B170" t="n">
-        <v>-0.7672008872032166</v>
+        <v>0.0008206855272874236</v>
       </c>
     </row>
     <row r="171">
@@ -1797,7 +1797,7 @@
         <v>181</v>
       </c>
       <c r="B171" t="n">
-        <v>-0.7412517070770264</v>
+        <v>0.0008769624982960522</v>
       </c>
     </row>
     <row r="172">
@@ -1805,7 +1805,7 @@
         <v>182</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.7066277265548706</v>
+        <v>0.0009167084353975952</v>
       </c>
     </row>
     <row r="173">
@@ -1813,7 +1813,7 @@
         <v>183</v>
       </c>
       <c r="B173" t="n">
-        <v>-0.792682945728302</v>
+        <v>0.001382965827360749</v>
       </c>
     </row>
     <row r="174">
@@ -1821,7 +1821,7 @@
         <v>184</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.6930413246154785</v>
+        <v>0.003819930134341121</v>
       </c>
     </row>
     <row r="175">
@@ -1829,7 +1829,7 @@
         <v>185</v>
       </c>
       <c r="B175" t="n">
-        <v>-0.6878577470779419</v>
+        <v>0.008229604922235012</v>
       </c>
     </row>
     <row r="176">
@@ -1837,7 +1837,7 @@
         <v>186</v>
       </c>
       <c r="B176" t="n">
-        <v>-0.7045717835426331</v>
+        <v>0.01287511549890041</v>
       </c>
     </row>
     <row r="177">
@@ -1845,7 +1845,7 @@
         <v>187</v>
       </c>
       <c r="B177" t="n">
-        <v>-0.7660784125328064</v>
+        <v>0.01519257295876741</v>
       </c>
     </row>
     <row r="178">
@@ -1853,7 +1853,7 @@
         <v>188</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.8321103453636169</v>
+        <v>0.01512176264077425</v>
       </c>
     </row>
     <row r="179">
@@ -1861,7 +1861,7 @@
         <v>189</v>
       </c>
       <c r="B179" t="n">
-        <v>-0.874809205532074</v>
+        <v>0.01242175884544849</v>
       </c>
     </row>
     <row r="180">
@@ -1869,7 +1869,7 @@
         <v>190</v>
       </c>
       <c r="B180" t="n">
-        <v>-0.7999387979507446</v>
+        <v>0.0150938369333744</v>
       </c>
     </row>
     <row r="181">
@@ -1877,7 +1877,7 @@
         <v>191</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.6746757030487061</v>
+        <v>0.02559294365346432</v>
       </c>
     </row>
     <row r="182">
@@ -1885,7 +1885,7 @@
         <v>192</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.6519678235054016</v>
+        <v>0.02569583989679813</v>
       </c>
     </row>
     <row r="183">
@@ -1893,7 +1893,7 @@
         <v>193</v>
       </c>
       <c r="B183" t="n">
-        <v>-0.5432583689689636</v>
+        <v>0.01864391565322876</v>
       </c>
     </row>
     <row r="184">
@@ -1901,7 +1901,7 @@
         <v>194</v>
       </c>
       <c r="B184" t="n">
-        <v>-0.5646163821220398</v>
+        <v>0.00494690053164959</v>
       </c>
     </row>
     <row r="185">
@@ -1909,7 +1909,7 @@
         <v>195</v>
       </c>
       <c r="B185" t="n">
-        <v>-0.4023584723472595</v>
+        <v>0.007243606261909008</v>
       </c>
     </row>
     <row r="186">
@@ -1917,7 +1917,7 @@
         <v>196</v>
       </c>
       <c r="B186" t="n">
-        <v>-0.252719908952713</v>
+        <v>0.01365439500659704</v>
       </c>
     </row>
     <row r="187">
@@ -1925,7 +1925,7 @@
         <v>197</v>
       </c>
       <c r="B187" t="n">
-        <v>-0.1058281511068344</v>
+        <v>0.01936949230730534</v>
       </c>
     </row>
     <row r="188">
@@ -1933,7 +1933,7 @@
         <v>198</v>
       </c>
       <c r="B188" t="n">
-        <v>-0.0711996853351593</v>
+        <v>0.02291315980255604</v>
       </c>
     </row>
     <row r="189">
@@ -1941,7 +1941,7 @@
         <v>199</v>
       </c>
       <c r="B189" t="n">
-        <v>-0.08672124147415161</v>
+        <v>0.01732055842876434</v>
       </c>
     </row>
     <row r="190">
@@ -1949,7 +1949,7 @@
         <v>200</v>
       </c>
       <c r="B190" t="n">
-        <v>-0.1204409301280975</v>
+        <v>0.01824280992150307</v>
       </c>
     </row>
     <row r="191">
@@ -1957,7 +1957,7 @@
         <v>201</v>
       </c>
       <c r="B191" t="n">
-        <v>-0.1716897636651993</v>
+        <v>0.01637599430978298</v>
       </c>
     </row>
     <row r="192">
@@ -1965,7 +1965,7 @@
         <v>202</v>
       </c>
       <c r="B192" t="n">
-        <v>-0.1725849062204361</v>
+        <v>0.0180769432336092</v>
       </c>
     </row>
     <row r="193">
@@ -1973,7 +1973,7 @@
         <v>203</v>
       </c>
       <c r="B193" t="n">
-        <v>-0.1861071437597275</v>
+        <v>0.03195123001933098</v>
       </c>
     </row>
     <row r="194">
@@ -1981,7 +1981,7 @@
         <v>204</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.3346488177776337</v>
+        <v>0.02323172241449356</v>
       </c>
     </row>
     <row r="195">
@@ -1989,7 +1989,7 @@
         <v>205</v>
       </c>
       <c r="B195" t="n">
-        <v>-0.3724211752414703</v>
+        <v>0.008121252059936523</v>
       </c>
     </row>
     <row r="196">
@@ -1997,7 +1997,7 @@
         <v>206</v>
       </c>
       <c r="B196" t="n">
-        <v>-0.4406965672969818</v>
+        <v>0.002761813346296549</v>
       </c>
     </row>
     <row r="197">
@@ -2005,7 +2005,7 @@
         <v>207</v>
       </c>
       <c r="B197" t="n">
-        <v>-0.5327703356742859</v>
+        <v>0.002047019312158227</v>
       </c>
     </row>
     <row r="198">
@@ -2013,7 +2013,7 @@
         <v>208</v>
       </c>
       <c r="B198" t="n">
-        <v>-0.586189329624176</v>
+        <v>0.001522595644928515</v>
       </c>
     </row>
     <row r="199">
@@ -2021,7 +2021,7 @@
         <v>209</v>
       </c>
       <c r="B199" t="n">
-        <v>-0.6757768988609314</v>
+        <v>0.00141706969588995</v>
       </c>
     </row>
     <row r="200">
@@ -2029,7 +2029,7 @@
         <v>210</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.6950279474258423</v>
+        <v>0.001162980333901942</v>
       </c>
     </row>
     <row r="201">
@@ -2037,7 +2037,7 @@
         <v>211</v>
       </c>
       <c r="B201" t="n">
-        <v>-0.7792893052101135</v>
+        <v>0.001339886453934014</v>
       </c>
     </row>
     <row r="202">
@@ -2045,7 +2045,7 @@
         <v>212</v>
       </c>
       <c r="B202" t="n">
-        <v>-0.8108713626861572</v>
+        <v>0.001246334402821958</v>
       </c>
     </row>
     <row r="203">
@@ -2053,7 +2053,7 @@
         <v>213</v>
       </c>
       <c r="B203" t="n">
-        <v>-0.8368619084358215</v>
+        <v>0.001136910985223949</v>
       </c>
     </row>
     <row r="204">
@@ -2061,7 +2061,7 @@
         <v>214</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.7487137913703918</v>
+        <v>0.001206033979542553</v>
       </c>
     </row>
     <row r="205">
@@ -2069,7 +2069,7 @@
         <v>215</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.6175974011421204</v>
+        <v>0.001507554086856544</v>
       </c>
     </row>
     <row r="206">
@@ -2077,7 +2077,7 @@
         <v>216</v>
       </c>
       <c r="B206" t="n">
-        <v>-0.5202260613441467</v>
+        <v>0.001784221734851599</v>
       </c>
     </row>
     <row r="207">
@@ -2085,7 +2085,7 @@
         <v>217</v>
       </c>
       <c r="B207" t="n">
-        <v>-0.3879847824573517</v>
+        <v>0.00205143284983933</v>
       </c>
     </row>
     <row r="208">
@@ -2093,7 +2093,7 @@
         <v>218</v>
       </c>
       <c r="B208" t="n">
-        <v>-0.2893206775188446</v>
+        <v>0.006727105472236872</v>
       </c>
     </row>
     <row r="209">
@@ -2101,7 +2101,7 @@
         <v>219</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.1334443241357803</v>
+        <v>0.04574079439043999</v>
       </c>
     </row>
     <row r="210">
@@ -2109,7 +2109,7 @@
         <v>220</v>
       </c>
       <c r="B210" t="n">
-        <v>-0.1768137812614441</v>
+        <v>0.04329484701156616</v>
       </c>
     </row>
     <row r="211">
@@ -2117,7 +2117,7 @@
         <v>221</v>
       </c>
       <c r="B211" t="n">
-        <v>-0.1663097441196442</v>
+        <v>0.05848336592316628</v>
       </c>
     </row>
     <row r="212">
@@ -2125,7 +2125,7 @@
         <v>222</v>
       </c>
       <c r="B212" t="n">
-        <v>-0.2681736052036285</v>
+        <v>0.02929470501840115</v>
       </c>
     </row>
     <row r="213">
@@ -2133,7 +2133,7 @@
         <v>223</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.3582539260387421</v>
+        <v>0.01759227178990841</v>
       </c>
     </row>
     <row r="214">
@@ -2141,7 +2141,7 @@
         <v>224</v>
       </c>
       <c r="B214" t="n">
-        <v>-0.4133841097354889</v>
+        <v>0.01125937979668379</v>
       </c>
     </row>
     <row r="215">
@@ -2149,7 +2149,7 @@
         <v>225</v>
       </c>
       <c r="B215" t="n">
-        <v>-0.5334569811820984</v>
+        <v>0.006386744324117899</v>
       </c>
     </row>
     <row r="216">
@@ -2157,7 +2157,7 @@
         <v>226</v>
       </c>
       <c r="B216" t="n">
-        <v>-0.6503228545188904</v>
+        <v>0.005074630491435528</v>
       </c>
     </row>
     <row r="217">
@@ -2165,7 +2165,7 @@
         <v>227</v>
       </c>
       <c r="B217" t="n">
-        <v>-0.7149304747581482</v>
+        <v>0.004536195658147335</v>
       </c>
     </row>
     <row r="218">
@@ -2173,7 +2173,7 @@
         <v>228</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.7592846155166626</v>
+        <v>0.002729195402935147</v>
       </c>
     </row>
     <row r="219">
@@ -2181,7 +2181,7 @@
         <v>229</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.6220402121543884</v>
+        <v>0.002212524646893144</v>
       </c>
     </row>
     <row r="220">
@@ -2189,7 +2189,7 @@
         <v>230</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.5138335227966309</v>
+        <v>0.001382388989441097</v>
       </c>
     </row>
     <row r="221">
@@ -2197,7 +2197,7 @@
         <v>231</v>
       </c>
       <c r="B221" t="n">
-        <v>-0.4919544756412506</v>
+        <v>0.001313357148319483</v>
       </c>
     </row>
     <row r="222">
@@ -2205,7 +2205,7 @@
         <v>232</v>
       </c>
       <c r="B222" t="n">
-        <v>-0.3451714813709259</v>
+        <v>0.001298068324103951</v>
       </c>
     </row>
     <row r="223">
@@ -2213,7 +2213,7 @@
         <v>233</v>
       </c>
       <c r="B223" t="n">
-        <v>-0.1600805968046188</v>
+        <v>0.001323366188444197</v>
       </c>
     </row>
     <row r="224">
@@ -2221,7 +2221,7 @@
         <v>234</v>
       </c>
       <c r="B224" t="n">
-        <v>-0.07164333015680313</v>
+        <v>0.001491399365477264</v>
       </c>
     </row>
     <row r="225">
@@ -2229,7 +2229,7 @@
         <v>235</v>
       </c>
       <c r="B225" t="n">
-        <v>-0.05276528000831604</v>
+        <v>0.001802572864107788</v>
       </c>
     </row>
     <row r="226">
@@ -2237,7 +2237,7 @@
         <v>236</v>
       </c>
       <c r="B226" t="n">
-        <v>-0.2638348042964935</v>
+        <v>0.001433437806554139</v>
       </c>
     </row>
     <row r="227">
@@ -2245,7 +2245,7 @@
         <v>237</v>
       </c>
       <c r="B227" t="n">
-        <v>-0.4058006405830383</v>
+        <v>0.001557060983031988</v>
       </c>
     </row>
     <row r="228">
@@ -2253,7 +2253,7 @@
         <v>238</v>
       </c>
       <c r="B228" t="n">
-        <v>-0.4956319034099579</v>
+        <v>0.00260878074914217</v>
       </c>
     </row>
     <row r="229">
@@ -2261,7 +2261,7 @@
         <v>239</v>
       </c>
       <c r="B229" t="n">
-        <v>-0.476317971944809</v>
+        <v>0.009330133907496929</v>
       </c>
     </row>
     <row r="230">
@@ -2269,7 +2269,7 @@
         <v>240</v>
       </c>
       <c r="B230" t="n">
-        <v>-0.642684280872345</v>
+        <v>0.01364374998956919</v>
       </c>
     </row>
     <row r="231">
@@ -2277,7 +2277,7 @@
         <v>241</v>
       </c>
       <c r="B231" t="n">
-        <v>-0.6127118468284607</v>
+        <v>0.014064677990973</v>
       </c>
     </row>
     <row r="232">
@@ -2285,7 +2285,7 @@
         <v>242</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.7714189291000366</v>
+        <v>0.01266301143914461</v>
       </c>
     </row>
     <row r="233">
@@ -2293,7 +2293,7 @@
         <v>243</v>
       </c>
       <c r="B233" t="n">
-        <v>-0.7325621247291565</v>
+        <v>0.02083219774067402</v>
       </c>
     </row>
     <row r="234">
@@ -2301,7 +2301,7 @@
         <v>244</v>
       </c>
       <c r="B234" t="n">
-        <v>-0.706570029258728</v>
+        <v>0.0282770749181509</v>
       </c>
     </row>
     <row r="235">
@@ -2309,7 +2309,7 @@
         <v>245</v>
       </c>
       <c r="B235" t="n">
-        <v>-0.7223668098449707</v>
+        <v>0.0428726002573967</v>
       </c>
     </row>
     <row r="236">
@@ -2317,7 +2317,7 @@
         <v>246</v>
       </c>
       <c r="B236" t="n">
-        <v>-0.7230458855628967</v>
+        <v>0.03664672374725342</v>
       </c>
     </row>
     <row r="237">
@@ -2325,7 +2325,7 @@
         <v>247</v>
       </c>
       <c r="B237" t="n">
-        <v>-0.6773681640625</v>
+        <v>0.0354069396853447</v>
       </c>
     </row>
     <row r="238">
@@ -2333,7 +2333,7 @@
         <v>248</v>
       </c>
       <c r="B238" t="n">
-        <v>-0.6412189602851868</v>
+        <v>0.02973768673837185</v>
       </c>
     </row>
     <row r="239">
@@ -2341,7 +2341,7 @@
         <v>249</v>
       </c>
       <c r="B239" t="n">
-        <v>-0.5273331999778748</v>
+        <v>0.03309768065810204</v>
       </c>
     </row>
     <row r="240">
@@ -2349,7 +2349,7 @@
         <v>250</v>
       </c>
       <c r="B240" t="n">
-        <v>-0.2246605753898621</v>
+        <v>0.05613384768366814</v>
       </c>
     </row>
     <row r="241">
@@ -2357,7 +2357,7 @@
         <v>251</v>
       </c>
       <c r="B241" t="n">
-        <v>0.2197372317314148</v>
+        <v>0.1593698859214783</v>
       </c>
     </row>
     <row r="242">
@@ -2365,7 +2365,7 @@
         <v>252</v>
       </c>
       <c r="B242" t="n">
-        <v>0.6488168835639954</v>
+        <v>0.4058735966682434</v>
       </c>
     </row>
     <row r="243">
@@ -2373,7 +2373,7 @@
         <v>253</v>
       </c>
       <c r="B243" t="n">
-        <v>0.8018750548362732</v>
+        <v>0.4510340988636017</v>
       </c>
     </row>
     <row r="244">
@@ -2381,7 +2381,7 @@
         <v>254</v>
       </c>
       <c r="B244" t="n">
-        <v>1.137859702110291</v>
+        <v>0.5069187879562378</v>
       </c>
     </row>
     <row r="245">
@@ -2389,7 +2389,7 @@
         <v>255</v>
       </c>
       <c r="B245" t="n">
-        <v>1.391830682754517</v>
+        <v>0.5640538930892944</v>
       </c>
     </row>
     <row r="246">
@@ -2397,7 +2397,7 @@
         <v>256</v>
       </c>
       <c r="B246" t="n">
-        <v>1.536111831665039</v>
+        <v>0.6014912128448486</v>
       </c>
     </row>
     <row r="247">
@@ -2405,7 +2405,7 @@
         <v>257</v>
       </c>
       <c r="B247" t="n">
-        <v>1.836000919342041</v>
+        <v>0.6731722354888916</v>
       </c>
     </row>
     <row r="248">
@@ -2413,7 +2413,7 @@
         <v>258</v>
       </c>
       <c r="B248" t="n">
-        <v>1.998657703399658</v>
+        <v>0.7003175616264343</v>
       </c>
     </row>
     <row r="249">
@@ -2421,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="B249" t="n">
-        <v>2.090697288513184</v>
+        <v>0.7004779577255249</v>
       </c>
     </row>
     <row r="250">
@@ -2429,7 +2429,7 @@
         <v>260</v>
       </c>
       <c r="B250" t="n">
-        <v>2.010653018951416</v>
+        <v>0.6944728493690491</v>
       </c>
     </row>
     <row r="251">
@@ -2437,7 +2437,7 @@
         <v>261</v>
       </c>
       <c r="B251" t="n">
-        <v>1.870157241821289</v>
+        <v>0.6606590151786804</v>
       </c>
     </row>
     <row r="252">
@@ -2445,7 +2445,7 @@
         <v>262</v>
       </c>
       <c r="B252" t="n">
-        <v>1.655340909957886</v>
+        <v>0.632301390171051</v>
       </c>
     </row>
     <row r="253">
@@ -2453,7 +2453,7 @@
         <v>263</v>
       </c>
       <c r="B253" t="n">
-        <v>1.5710529088974</v>
+        <v>0.6501938104629517</v>
       </c>
     </row>
     <row r="254">
@@ -2461,7 +2461,7 @@
         <v>264</v>
       </c>
       <c r="B254" t="n">
-        <v>1.094658374786377</v>
+        <v>0.5824760794639587</v>
       </c>
     </row>
     <row r="255">
@@ -2469,7 +2469,7 @@
         <v>265</v>
       </c>
       <c r="B255" t="n">
-        <v>0.5010871291160583</v>
+        <v>0.4356453120708466</v>
       </c>
     </row>
     <row r="256">
@@ -2477,7 +2477,7 @@
         <v>266</v>
       </c>
       <c r="B256" t="n">
-        <v>0.1035108715295792</v>
+        <v>0.2353198081254959</v>
       </c>
     </row>
     <row r="257">
@@ -2485,7 +2485,7 @@
         <v>267</v>
       </c>
       <c r="B257" t="n">
-        <v>-0.1603571027517319</v>
+        <v>0.122534804046154</v>
       </c>
     </row>
     <row r="258">
@@ -2493,7 +2493,7 @@
         <v>268</v>
       </c>
       <c r="B258" t="n">
-        <v>-0.2162807136774063</v>
+        <v>0.08238466829061508</v>
       </c>
     </row>
     <row r="259">
@@ -2501,7 +2501,7 @@
         <v>269</v>
       </c>
       <c r="B259" t="n">
-        <v>-0.2880776822566986</v>
+        <v>0.04616615176200867</v>
       </c>
     </row>
     <row r="260">
@@ -2509,7 +2509,7 @@
         <v>270</v>
       </c>
       <c r="B260" t="n">
-        <v>-0.3182109296321869</v>
+        <v>0.03609159588813782</v>
       </c>
     </row>
     <row r="261">
@@ -2517,7 +2517,7 @@
         <v>271</v>
       </c>
       <c r="B261" t="n">
-        <v>-0.4211650192737579</v>
+        <v>0.02146651595830917</v>
       </c>
     </row>
     <row r="262">
@@ -2525,7 +2525,7 @@
         <v>272</v>
       </c>
       <c r="B262" t="n">
-        <v>-0.5381391048431396</v>
+        <v>0.01253515388816595</v>
       </c>
     </row>
     <row r="263">
@@ -2533,7 +2533,7 @@
         <v>273</v>
       </c>
       <c r="B263" t="n">
-        <v>-0.6579938530921936</v>
+        <v>0.005653326399624348</v>
       </c>
     </row>
     <row r="264">
@@ -2541,7 +2541,7 @@
         <v>274</v>
       </c>
       <c r="B264" t="n">
-        <v>-0.7608873248100281</v>
+        <v>0.004405037499964237</v>
       </c>
     </row>
     <row r="265">
@@ -2549,7 +2549,7 @@
         <v>275</v>
       </c>
       <c r="B265" t="n">
-        <v>-0.7800555229187012</v>
+        <v>0.004921145737171173</v>
       </c>
     </row>
     <row r="266">
@@ -2557,7 +2557,7 @@
         <v>276</v>
       </c>
       <c r="B266" t="n">
-        <v>-0.816286563873291</v>
+        <v>0.005237048957496881</v>
       </c>
     </row>
     <row r="267">
@@ -2565,7 +2565,7 @@
         <v>277</v>
       </c>
       <c r="B267" t="n">
-        <v>-0.9229026436805725</v>
+        <v>0.003984578419476748</v>
       </c>
     </row>
     <row r="268">
@@ -2573,7 +2573,7 @@
         <v>278</v>
       </c>
       <c r="B268" t="n">
-        <v>-1.07415759563446</v>
+        <v>0.003617219626903534</v>
       </c>
     </row>
     <row r="269">
@@ -2581,7 +2581,7 @@
         <v>279</v>
       </c>
       <c r="B269" t="n">
-        <v>-1.198561429977417</v>
+        <v>0.003475874429568648</v>
       </c>
     </row>
     <row r="270">
@@ -2589,7 +2589,7 @@
         <v>280</v>
       </c>
       <c r="B270" t="n">
-        <v>-1.245152235031128</v>
+        <v>0.003519295714795589</v>
       </c>
     </row>
     <row r="271">
@@ -2597,7 +2597,7 @@
         <v>281</v>
       </c>
       <c r="B271" t="n">
-        <v>-1.21546745300293</v>
+        <v>0.002928961301222444</v>
       </c>
     </row>
     <row r="272">
@@ -2605,7 +2605,7 @@
         <v>282</v>
       </c>
       <c r="B272" t="n">
-        <v>-1.155220031738281</v>
+        <v>0.00211519468575716</v>
       </c>
     </row>
     <row r="273">
@@ -2613,7 +2613,7 @@
         <v>283</v>
       </c>
       <c r="B273" t="n">
-        <v>-1.119848966598511</v>
+        <v>0.00171635253354907</v>
       </c>
     </row>
     <row r="274">
@@ -2621,7 +2621,7 @@
         <v>284</v>
       </c>
       <c r="B274" t="n">
-        <v>-1.031433463096619</v>
+        <v>0.001369846286252141</v>
       </c>
     </row>
     <row r="275">
@@ -2629,7 +2629,7 @@
         <v>285</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.9274649024009705</v>
+        <v>0.001277229748666286</v>
       </c>
     </row>
     <row r="276">
@@ -2637,7 +2637,7 @@
         <v>286</v>
       </c>
       <c r="B276" t="n">
-        <v>-0.7784988284111023</v>
+        <v>0.00139982404652983</v>
       </c>
     </row>
     <row r="277">
@@ -2645,7 +2645,7 @@
         <v>287</v>
       </c>
       <c r="B277" t="n">
-        <v>-0.5844765305519104</v>
+        <v>0.001752703101374209</v>
       </c>
     </row>
     <row r="278">
@@ -2653,7 +2653,7 @@
         <v>288</v>
       </c>
       <c r="B278" t="n">
-        <v>-0.3859623372554779</v>
+        <v>0.002629354130476713</v>
       </c>
     </row>
     <row r="279">
@@ -2661,7 +2661,7 @@
         <v>289</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.373862087726593</v>
+        <v>0.005154227837920189</v>
       </c>
     </row>
     <row r="280">
@@ -2669,7 +2669,7 @@
         <v>290</v>
       </c>
       <c r="B280" t="n">
-        <v>-0.4340192675590515</v>
+        <v>0.003450990188866854</v>
       </c>
     </row>
     <row r="281">
@@ -2677,7 +2677,7 @@
         <v>291</v>
       </c>
       <c r="B281" t="n">
-        <v>-0.38295978307724</v>
+        <v>0.001610721577890217</v>
       </c>
     </row>
     <row r="282">
@@ -2685,7 +2685,7 @@
         <v>292</v>
       </c>
       <c r="B282" t="n">
-        <v>-0.3409624993801117</v>
+        <v>0.001165231107734144</v>
       </c>
     </row>
     <row r="283">
@@ -2693,7 +2693,7 @@
         <v>293</v>
       </c>
       <c r="B283" t="n">
-        <v>-0.2926874458789825</v>
+        <v>0.001229131710715592</v>
       </c>
     </row>
     <row r="284">
@@ -2701,7 +2701,7 @@
         <v>294</v>
       </c>
       <c r="B284" t="n">
-        <v>-0.256678432226181</v>
+        <v>0.001405089977197349</v>
       </c>
     </row>
     <row r="285">
@@ -2709,7 +2709,7 @@
         <v>295</v>
       </c>
       <c r="B285" t="n">
-        <v>-0.2265707701444626</v>
+        <v>0.002184665994718671</v>
       </c>
     </row>
     <row r="286">
@@ -2717,7 +2717,7 @@
         <v>296</v>
       </c>
       <c r="B286" t="n">
-        <v>-0.2584448754787445</v>
+        <v>0.002095256233587861</v>
       </c>
     </row>
     <row r="287">
@@ -2725,7 +2725,7 @@
         <v>297</v>
       </c>
       <c r="B287" t="n">
-        <v>-0.3065916895866394</v>
+        <v>0.001906689954921603</v>
       </c>
     </row>
     <row r="288">
@@ -2733,7 +2733,7 @@
         <v>298</v>
       </c>
       <c r="B288" t="n">
-        <v>-0.3191056251525879</v>
+        <v>0.002598759019747376</v>
       </c>
     </row>
     <row r="289">
@@ -2741,7 +2741,7 @@
         <v>299</v>
       </c>
       <c r="B289" t="n">
-        <v>-0.2041188776493073</v>
+        <v>0.004748132545500994</v>
       </c>
     </row>
     <row r="290">
@@ -2749,7 +2749,7 @@
         <v>300</v>
       </c>
       <c r="B290" t="n">
-        <v>-0.1944680958986282</v>
+        <v>0.005999397486448288</v>
       </c>
     </row>
     <row r="291">
@@ -2757,7 +2757,7 @@
         <v>301</v>
       </c>
       <c r="B291" t="n">
-        <v>-0.2180643677711487</v>
+        <v>0.006436426192522049</v>
       </c>
     </row>
     <row r="292">
@@ -2765,7 +2765,7 @@
         <v>302</v>
       </c>
       <c r="B292" t="n">
-        <v>-0.4051418602466583</v>
+        <v>0.004451987333595753</v>
       </c>
     </row>
     <row r="293">
@@ -2773,7 +2773,7 @@
         <v>303</v>
       </c>
       <c r="B293" t="n">
-        <v>-0.4757617712020874</v>
+        <v>0.003308413783088326</v>
       </c>
     </row>
     <row r="294">
@@ -2781,7 +2781,7 @@
         <v>304</v>
       </c>
       <c r="B294" t="n">
-        <v>-0.4501419961452484</v>
+        <v>0.002762746997177601</v>
       </c>
     </row>
     <row r="295">
@@ -2789,7 +2789,7 @@
         <v>305</v>
       </c>
       <c r="B295" t="n">
-        <v>-0.3392676115036011</v>
+        <v>0.002368289511650801</v>
       </c>
     </row>
     <row r="296">
@@ -2797,7 +2797,7 @@
         <v>306</v>
       </c>
       <c r="B296" t="n">
-        <v>-0.2957948446273804</v>
+        <v>0.002646871376782656</v>
       </c>
     </row>
     <row r="297">
@@ -2805,7 +2805,7 @@
         <v>307</v>
       </c>
       <c r="B297" t="n">
-        <v>-0.2763522267341614</v>
+        <v>0.003290464635938406</v>
       </c>
     </row>
     <row r="298">
@@ -2813,7 +2813,7 @@
         <v>308</v>
       </c>
       <c r="B298" t="n">
-        <v>-0.3580902218818665</v>
+        <v>0.002281593857333064</v>
       </c>
     </row>
     <row r="299">
@@ -2821,7 +2821,7 @@
         <v>309</v>
       </c>
       <c r="B299" t="n">
-        <v>-0.4606879651546478</v>
+        <v>0.001491616130806506</v>
       </c>
     </row>
     <row r="300">
@@ -2829,7 +2829,7 @@
         <v>310</v>
       </c>
       <c r="B300" t="n">
-        <v>-0.4898342788219452</v>
+        <v>0.00120313058141619</v>
       </c>
     </row>
     <row r="301">
@@ -2837,7 +2837,7 @@
         <v>311</v>
       </c>
       <c r="B301" t="n">
-        <v>-0.4843361675739288</v>
+        <v>0.001027395366691053</v>
       </c>
     </row>
     <row r="302">
@@ -2845,7 +2845,7 @@
         <v>312</v>
       </c>
       <c r="B302" t="n">
-        <v>-0.5410914421081543</v>
+        <v>0.0009802824351936579</v>
       </c>
     </row>
     <row r="303">
@@ -2853,7 +2853,7 @@
         <v>313</v>
       </c>
       <c r="B303" t="n">
-        <v>-0.6921359300613403</v>
+        <v>0.0009890206856653094</v>
       </c>
     </row>
     <row r="304">
@@ -2861,7 +2861,7 @@
         <v>314</v>
       </c>
       <c r="B304" t="n">
-        <v>-0.8119251132011414</v>
+        <v>0.001106849522329867</v>
       </c>
     </row>
     <row r="305">
@@ -2869,7 +2869,7 @@
         <v>315</v>
       </c>
       <c r="B305" t="n">
-        <v>-0.9219204187393188</v>
+        <v>0.001263212179765105</v>
       </c>
     </row>
     <row r="306">
@@ -2877,7 +2877,7 @@
         <v>316</v>
       </c>
       <c r="B306" t="n">
-        <v>-0.9016334414482117</v>
+        <v>0.00164490076713264</v>
       </c>
     </row>
     <row r="307">
@@ -2885,7 +2885,7 @@
         <v>317</v>
       </c>
       <c r="B307" t="n">
-        <v>-0.8956494927406311</v>
+        <v>0.001788855297490954</v>
       </c>
     </row>
     <row r="308">
@@ -2893,7 +2893,7 @@
         <v>318</v>
       </c>
       <c r="B308" t="n">
-        <v>-0.838320791721344</v>
+        <v>0.002226686105132103</v>
       </c>
     </row>
     <row r="309">
@@ -2901,7 +2901,7 @@
         <v>319</v>
       </c>
       <c r="B309" t="n">
-        <v>-0.8027639985084534</v>
+        <v>0.002301257569342852</v>
       </c>
     </row>
     <row r="310">
@@ -2909,7 +2909,7 @@
         <v>320</v>
       </c>
       <c r="B310" t="n">
-        <v>-0.7879776954650879</v>
+        <v>0.00203690305352211</v>
       </c>
     </row>
     <row r="311">
@@ -2917,7 +2917,7 @@
         <v>321</v>
       </c>
       <c r="B311" t="n">
-        <v>-0.7754724025726318</v>
+        <v>0.001700786524452269</v>
       </c>
     </row>
     <row r="312">
@@ -2925,7 +2925,7 @@
         <v>322</v>
       </c>
       <c r="B312" t="n">
-        <v>-0.7359232306480408</v>
+        <v>0.001654825056903064</v>
       </c>
     </row>
     <row r="313">
@@ -2933,7 +2933,7 @@
         <v>323</v>
       </c>
       <c r="B313" t="n">
-        <v>-0.6272628307342529</v>
+        <v>0.002118337200954556</v>
       </c>
     </row>
     <row r="314">
@@ -2941,7 +2941,7 @@
         <v>324</v>
       </c>
       <c r="B314" t="n">
-        <v>-0.5241251587867737</v>
+        <v>0.005745469126850367</v>
       </c>
     </row>
     <row r="315">
@@ -2949,7 +2949,7 @@
         <v>325</v>
       </c>
       <c r="B315" t="n">
-        <v>-0.6458650231361389</v>
+        <v>0.006768902763724327</v>
       </c>
     </row>
     <row r="316">
@@ -2957,7 +2957,7 @@
         <v>326</v>
       </c>
       <c r="B316" t="n">
-        <v>-0.7595148086547852</v>
+        <v>0.004483329597860575</v>
       </c>
     </row>
     <row r="317">
@@ -2965,7 +2965,7 @@
         <v>327</v>
       </c>
       <c r="B317" t="n">
-        <v>-0.8113442063331604</v>
+        <v>0.003478572936728597</v>
       </c>
     </row>
     <row r="318">
@@ -2973,7 +2973,7 @@
         <v>328</v>
       </c>
       <c r="B318" t="n">
-        <v>-0.7893009781837463</v>
+        <v>0.002932855859398842</v>
       </c>
     </row>
     <row r="319">
@@ -2981,7 +2981,7 @@
         <v>329</v>
       </c>
       <c r="B319" t="n">
-        <v>-0.714442253112793</v>
+        <v>0.002806687261909246</v>
       </c>
     </row>
     <row r="320">
@@ -2989,7 +2989,7 @@
         <v>330</v>
       </c>
       <c r="B320" t="n">
-        <v>-0.6115860342979431</v>
+        <v>0.003270562738180161</v>
       </c>
     </row>
     <row r="321">
@@ -2997,7 +2997,7 @@
         <v>331</v>
       </c>
       <c r="B321" t="n">
-        <v>-0.5309810638427734</v>
+        <v>0.003208623034879565</v>
       </c>
     </row>
     <row r="322">
@@ -3005,7 +3005,7 @@
         <v>332</v>
       </c>
       <c r="B322" t="n">
-        <v>-0.4605094194412231</v>
+        <v>0.003020151751115918</v>
       </c>
     </row>
     <row r="323">
@@ -3013,7 +3013,7 @@
         <v>333</v>
       </c>
       <c r="B323" t="n">
-        <v>-0.4420614540576935</v>
+        <v>0.002453463384881616</v>
       </c>
     </row>
     <row r="324">
@@ -3021,7 +3021,7 @@
         <v>334</v>
       </c>
       <c r="B324" t="n">
-        <v>-0.4608222246170044</v>
+        <v>0.002026854082942009</v>
       </c>
     </row>
     <row r="325">
@@ -3029,7 +3029,7 @@
         <v>335</v>
       </c>
       <c r="B325" t="n">
-        <v>-0.4335678815841675</v>
+        <v>0.002217933535575867</v>
       </c>
     </row>
     <row r="326">
@@ -3037,7 +3037,7 @@
         <v>336</v>
       </c>
       <c r="B326" t="n">
-        <v>-0.4726569354534149</v>
+        <v>0.002959801349788904</v>
       </c>
     </row>
     <row r="327">
@@ -3045,7 +3045,7 @@
         <v>337</v>
       </c>
       <c r="B327" t="n">
-        <v>-0.5639836192131042</v>
+        <v>0.003643988398835063</v>
       </c>
     </row>
     <row r="328">
@@ -3053,7 +3053,7 @@
         <v>338</v>
       </c>
       <c r="B328" t="n">
-        <v>-0.6142714023590088</v>
+        <v>0.003076141234487295</v>
       </c>
     </row>
     <row r="329">
@@ -3061,7 +3061,7 @@
         <v>339</v>
       </c>
       <c r="B329" t="n">
-        <v>-0.6343997120857239</v>
+        <v>0.001802061568014324</v>
       </c>
     </row>
     <row r="330">
@@ -3069,7 +3069,7 @@
         <v>340</v>
       </c>
       <c r="B330" t="n">
-        <v>-0.5890000462532043</v>
+        <v>0.001237084507010877</v>
       </c>
     </row>
     <row r="331">
@@ -3077,7 +3077,7 @@
         <v>341</v>
       </c>
       <c r="B331" t="n">
-        <v>-0.6164456605911255</v>
+        <v>0.001173764932900667</v>
       </c>
     </row>
     <row r="332">
@@ -3085,7 +3085,7 @@
         <v>342</v>
       </c>
       <c r="B332" t="n">
-        <v>-0.68145352602005</v>
+        <v>0.001029899111017585</v>
       </c>
     </row>
     <row r="333">
@@ -3093,7 +3093,7 @@
         <v>343</v>
       </c>
       <c r="B333" t="n">
-        <v>-0.7960432767868042</v>
+        <v>0.001097141648642719</v>
       </c>
     </row>
     <row r="334">
@@ -3101,7 +3101,7 @@
         <v>344</v>
       </c>
       <c r="B334" t="n">
-        <v>-0.9184396862983704</v>
+        <v>0.00112570496276021</v>
       </c>
     </row>
     <row r="335">
@@ -3109,7 +3109,7 @@
         <v>345</v>
       </c>
       <c r="B335" t="n">
-        <v>-1.022146940231323</v>
+        <v>0.001119445427320898</v>
       </c>
     </row>
     <row r="336">
@@ -3117,7 +3117,7 @@
         <v>346</v>
       </c>
       <c r="B336" t="n">
-        <v>-1.010617733001709</v>
+        <v>0.001594649278558791</v>
       </c>
     </row>
     <row r="337">
@@ -3125,7 +3125,7 @@
         <v>347</v>
       </c>
       <c r="B337" t="n">
-        <v>-0.9216384291648865</v>
+        <v>0.003702468937262893</v>
       </c>
     </row>
     <row r="338">
@@ -3133,7 +3133,7 @@
         <v>348</v>
       </c>
       <c r="B338" t="n">
-        <v>-0.8761518597602844</v>
+        <v>0.01057783979922533</v>
       </c>
     </row>
     <row r="339">
@@ -3141,7 +3141,7 @@
         <v>349</v>
       </c>
       <c r="B339" t="n">
-        <v>-0.9581617116928101</v>
+        <v>0.0136325266212225</v>
       </c>
     </row>
     <row r="340">
@@ -3149,7 +3149,7 @@
         <v>350</v>
       </c>
       <c r="B340" t="n">
-        <v>-1.057127594947815</v>
+        <v>0.01696980930864811</v>
       </c>
     </row>
     <row r="341">
@@ -3157,7 +3157,7 @@
         <v>351</v>
       </c>
       <c r="B341" t="n">
-        <v>-1.00920581817627</v>
+        <v>0.02129585668444633</v>
       </c>
     </row>
     <row r="342">
@@ -3165,7 +3165,7 @@
         <v>352</v>
       </c>
       <c r="B342" t="n">
-        <v>-0.9474888443946838</v>
+        <v>0.02072001993656158</v>
       </c>
     </row>
     <row r="343">
@@ -3173,7 +3173,7 @@
         <v>353</v>
       </c>
       <c r="B343" t="n">
-        <v>-0.8398014903068542</v>
+        <v>0.02912547625601292</v>
       </c>
     </row>
     <row r="344">
@@ -3181,7 +3181,7 @@
         <v>354</v>
       </c>
       <c r="B344" t="n">
-        <v>-0.70725017786026</v>
+        <v>0.02365423552691936</v>
       </c>
     </row>
     <row r="345">
@@ -3189,7 +3189,7 @@
         <v>355</v>
       </c>
       <c r="B345" t="n">
-        <v>-0.5711231827735901</v>
+        <v>0.02048076502978802</v>
       </c>
     </row>
     <row r="346">
@@ -3197,7 +3197,7 @@
         <v>356</v>
       </c>
       <c r="B346" t="n">
-        <v>-0.4888936877250671</v>
+        <v>0.01172605063766241</v>
       </c>
     </row>
     <row r="347">
@@ -3205,7 +3205,7 @@
         <v>357</v>
       </c>
       <c r="B347" t="n">
-        <v>-0.4476036727428436</v>
+        <v>0.006762173492461443</v>
       </c>
     </row>
     <row r="348">
@@ -3213,7 +3213,7 @@
         <v>358</v>
       </c>
       <c r="B348" t="n">
-        <v>-0.4119292199611664</v>
+        <v>0.004579759668558836</v>
       </c>
     </row>
     <row r="349">
@@ -3221,7 +3221,7 @@
         <v>359</v>
       </c>
       <c r="B349" t="n">
-        <v>-0.317804753780365</v>
+        <v>0.003735965117812157</v>
       </c>
     </row>
     <row r="350">
@@ -3229,7 +3229,7 @@
         <v>360</v>
       </c>
       <c r="B350" t="n">
-        <v>-0.3309686481952667</v>
+        <v>0.002229662612080574</v>
       </c>
     </row>
     <row r="351">
@@ -3237,7 +3237,7 @@
         <v>361</v>
       </c>
       <c r="B351" t="n">
-        <v>-0.2890380918979645</v>
+        <v>0.001594640896655619</v>
       </c>
     </row>
     <row r="352">
@@ -3245,7 +3245,7 @@
         <v>362</v>
       </c>
       <c r="B352" t="n">
-        <v>-0.3384767770767212</v>
+        <v>0.0009976963046938181</v>
       </c>
     </row>
     <row r="353">
@@ -3253,7 +3253,7 @@
         <v>363</v>
       </c>
       <c r="B353" t="n">
-        <v>-0.3530508577823639</v>
+        <v>0.000838327978271991</v>
       </c>
     </row>
     <row r="354">
@@ -3261,7 +3261,7 @@
         <v>364</v>
       </c>
       <c r="B354" t="n">
-        <v>-0.2784462571144104</v>
+        <v>0.0008443816332146525</v>
       </c>
     </row>
     <row r="355">
@@ -3269,7 +3269,7 @@
         <v>365</v>
       </c>
       <c r="B355" t="n">
-        <v>-0.1856230050325394</v>
+        <v>0.0009276597993448377</v>
       </c>
     </row>
     <row r="356">
@@ -3277,7 +3277,7 @@
         <v>366</v>
       </c>
       <c r="B356" t="n">
-        <v>-0.1605732440948486</v>
+        <v>0.001124359550885856</v>
       </c>
     </row>
     <row r="357">
@@ -3285,7 +3285,7 @@
         <v>367</v>
       </c>
       <c r="B357" t="n">
-        <v>-0.1710937470197678</v>
+        <v>0.001278544776141644</v>
       </c>
     </row>
     <row r="358">
@@ -3293,7 +3293,7 @@
         <v>368</v>
       </c>
       <c r="B358" t="n">
-        <v>-0.2964026927947998</v>
+        <v>0.001181504805572331</v>
       </c>
     </row>
     <row r="359">
@@ -3301,7 +3301,7 @@
         <v>369</v>
       </c>
       <c r="B359" t="n">
-        <v>-0.4051311910152435</v>
+        <v>0.001504483516328037</v>
       </c>
     </row>
     <row r="360">
@@ -3309,7 +3309,7 @@
         <v>370</v>
       </c>
       <c r="B360" t="n">
-        <v>-0.525864839553833</v>
+        <v>0.002073503099381924</v>
       </c>
     </row>
     <row r="361">
@@ -3317,7 +3317,7 @@
         <v>371</v>
       </c>
       <c r="B361" t="n">
-        <v>-0.5722782015800476</v>
+        <v>0.004508161451667547</v>
       </c>
     </row>
     <row r="362">
@@ -3325,7 +3325,7 @@
         <v>372</v>
       </c>
       <c r="B362" t="n">
-        <v>-0.6100835800170898</v>
+        <v>0.009433174505829811</v>
       </c>
     </row>
     <row r="363">
@@ -3333,7 +3333,7 @@
         <v>373</v>
       </c>
       <c r="B363" t="n">
-        <v>-0.759598970413208</v>
+        <v>0.006064945366233587</v>
       </c>
     </row>
     <row r="364">
@@ -3341,7 +3341,7 @@
         <v>374</v>
       </c>
       <c r="B364" t="n">
-        <v>-0.9018222689628601</v>
+        <v>0.004987126681953669</v>
       </c>
     </row>
     <row r="365">
@@ -3349,7 +3349,7 @@
         <v>375</v>
       </c>
       <c r="B365" t="n">
-        <v>-0.984503448009491</v>
+        <v>0.004427046980708838</v>
       </c>
     </row>
     <row r="366">
@@ -3357,7 +3357,7 @@
         <v>376</v>
       </c>
       <c r="B366" t="n">
-        <v>-1.014571309089661</v>
+        <v>0.004051331896334887</v>
       </c>
     </row>
     <row r="367">
@@ -3365,7 +3365,7 @@
         <v>377</v>
       </c>
       <c r="B367" t="n">
-        <v>-1.02632474899292</v>
+        <v>0.00459468737244606</v>
       </c>
     </row>
     <row r="368">
@@ -3373,7 +3373,7 @@
         <v>378</v>
       </c>
       <c r="B368" t="n">
-        <v>-0.9327012896537781</v>
+        <v>0.003743974026292562</v>
       </c>
     </row>
     <row r="369">
@@ -3381,7 +3381,7 @@
         <v>379</v>
       </c>
       <c r="B369" t="n">
-        <v>-0.868876039981842</v>
+        <v>0.003015232738107443</v>
       </c>
     </row>
     <row r="370">
@@ -3389,7 +3389,7 @@
         <v>380</v>
       </c>
       <c r="B370" t="n">
-        <v>-0.8164188265800476</v>
+        <v>0.002096853917464614</v>
       </c>
     </row>
     <row r="371">
@@ -3397,7 +3397,7 @@
         <v>381</v>
       </c>
       <c r="B371" t="n">
-        <v>-0.798778235912323</v>
+        <v>0.001691631157882512</v>
       </c>
     </row>
     <row r="372">
@@ -3405,7 +3405,7 @@
         <v>382</v>
       </c>
       <c r="B372" t="n">
-        <v>-0.6894556283950806</v>
+        <v>0.001739116385579109</v>
       </c>
     </row>
     <row r="373">
@@ -3413,7 +3413,7 @@
         <v>383</v>
       </c>
       <c r="B373" t="n">
-        <v>-0.4964648187160492</v>
+        <v>0.002316690981388092</v>
       </c>
     </row>
     <row r="374">
@@ -3421,7 +3421,7 @@
         <v>384</v>
       </c>
       <c r="B374" t="n">
-        <v>-0.2914079129695892</v>
+        <v>0.004114237148314714</v>
       </c>
     </row>
     <row r="375">
@@ -3429,7 +3429,7 @@
         <v>385</v>
       </c>
       <c r="B375" t="n">
-        <v>-0.313988208770752</v>
+        <v>0.01462653744965792</v>
       </c>
     </row>
     <row r="376">
@@ -3437,7 +3437,7 @@
         <v>386</v>
       </c>
       <c r="B376" t="n">
-        <v>-0.297274649143219</v>
+        <v>0.02300018444657326</v>
       </c>
     </row>
     <row r="377">
@@ -3445,7 +3445,7 @@
         <v>387</v>
       </c>
       <c r="B377" t="n">
-        <v>-0.1716942638158798</v>
+        <v>0.01990692317485809</v>
       </c>
     </row>
     <row r="378">
@@ -3453,7 +3453,7 @@
         <v>388</v>
       </c>
       <c r="B378" t="n">
-        <v>-0.02884105406701565</v>
+        <v>0.01799619384109974</v>
       </c>
     </row>
     <row r="379">
@@ -3461,7 +3461,7 @@
         <v>389</v>
       </c>
       <c r="B379" t="n">
-        <v>0.1439626663923264</v>
+        <v>0.07086411863565445</v>
       </c>
     </row>
     <row r="380">
@@ -3469,7 +3469,7 @@
         <v>390</v>
       </c>
       <c r="B380" t="n">
-        <v>0.2918119728565216</v>
+        <v>0.2021597623825073</v>
       </c>
     </row>
     <row r="381">
@@ -3477,7 +3477,7 @@
         <v>391</v>
       </c>
       <c r="B381" t="n">
-        <v>0.4426704347133636</v>
+        <v>0.4223620593547821</v>
       </c>
     </row>
     <row r="382">
@@ -3485,7 +3485,7 @@
         <v>392</v>
       </c>
       <c r="B382" t="n">
-        <v>0.390709787607193</v>
+        <v>0.5330067873001099</v>
       </c>
     </row>
     <row r="383">
@@ -3493,7 +3493,7 @@
         <v>393</v>
       </c>
       <c r="B383" t="n">
-        <v>0.2833634316921234</v>
+        <v>0.5696646571159363</v>
       </c>
     </row>
     <row r="384">
@@ -3501,7 +3501,7 @@
         <v>394</v>
       </c>
       <c r="B384" t="n">
-        <v>0.2160288244485855</v>
+        <v>0.5975170731544495</v>
       </c>
     </row>
     <row r="385">
@@ -3509,7 +3509,7 @@
         <v>395</v>
       </c>
       <c r="B385" t="n">
-        <v>0.2088616490364075</v>
+        <v>0.6035223603248596</v>
       </c>
     </row>
     <row r="386">
@@ -3517,7 +3517,7 @@
         <v>396</v>
       </c>
       <c r="B386" t="n">
-        <v>-1.158379018306732e-05</v>
+        <v>0.5337416529655457</v>
       </c>
     </row>
     <row r="387">
@@ -3525,7 +3525,7 @@
         <v>397</v>
       </c>
       <c r="B387" t="n">
-        <v>-0.09751506894826889</v>
+        <v>0.4665830433368683</v>
       </c>
     </row>
     <row r="388">
@@ -3533,7 +3533,7 @@
         <v>398</v>
       </c>
       <c r="B388" t="n">
-        <v>-0.257536917924881</v>
+        <v>0.2815321087837219</v>
       </c>
     </row>
     <row r="389">
@@ -3541,7 +3541,7 @@
         <v>399</v>
       </c>
       <c r="B389" t="n">
-        <v>-0.3967768251895905</v>
+        <v>0.1419140100479126</v>
       </c>
     </row>
     <row r="390">
@@ -3549,7 +3549,7 @@
         <v>400</v>
       </c>
       <c r="B390" t="n">
-        <v>-0.4415239989757538</v>
+        <v>0.08561152219772339</v>
       </c>
     </row>
     <row r="391">
@@ -3557,7 +3557,7 @@
         <v>401</v>
       </c>
       <c r="B391" t="n">
-        <v>-0.4928832948207855</v>
+        <v>0.04317276179790497</v>
       </c>
     </row>
     <row r="392">
@@ -3565,7 +3565,7 @@
         <v>402</v>
       </c>
       <c r="B392" t="n">
-        <v>-0.4815804660320282</v>
+        <v>0.03822749853134155</v>
       </c>
     </row>
     <row r="393">
@@ -3573,7 +3573,7 @@
         <v>403</v>
       </c>
       <c r="B393" t="n">
-        <v>-0.5389502644538879</v>
+        <v>0.02661942131817341</v>
       </c>
     </row>
     <row r="394">
@@ -3581,7 +3581,7 @@
         <v>404</v>
       </c>
       <c r="B394" t="n">
-        <v>-0.699873685836792</v>
+        <v>0.018208347260952</v>
       </c>
     </row>
     <row r="395">
@@ -3589,7 +3589,7 @@
         <v>405</v>
       </c>
       <c r="B395" t="n">
-        <v>-0.8456225991249084</v>
+        <v>0.01059451140463352</v>
       </c>
     </row>
     <row r="396">
@@ -3597,7 +3597,7 @@
         <v>406</v>
       </c>
       <c r="B396" t="n">
-        <v>-0.9798310399055481</v>
+        <v>0.008503179997205734</v>
       </c>
     </row>
     <row r="397">
@@ -3605,7 +3605,7 @@
         <v>407</v>
       </c>
       <c r="B397" t="n">
-        <v>-1.055628418922424</v>
+        <v>0.008689818903803825</v>
       </c>
     </row>
     <row r="398">
@@ -3613,7 +3613,7 @@
         <v>408</v>
       </c>
       <c r="B398" t="n">
-        <v>-1.106721162796021</v>
+        <v>0.008430461399257183</v>
       </c>
     </row>
     <row r="399">
@@ -3621,7 +3621,7 @@
         <v>409</v>
       </c>
       <c r="B399" t="n">
-        <v>-1.031704306602478</v>
+        <v>0.005383600015193224</v>
       </c>
     </row>
     <row r="400">
@@ -3629,7 +3629,7 @@
         <v>410</v>
       </c>
       <c r="B400" t="n">
-        <v>-1.099912762641907</v>
+        <v>0.004335164092481136</v>
       </c>
     </row>
     <row r="401">
@@ -3637,7 +3637,7 @@
         <v>411</v>
       </c>
       <c r="B401" t="n">
-        <v>-1.170481562614441</v>
+        <v>0.003594493959099054</v>
       </c>
     </row>
     <row r="402">
@@ -3645,7 +3645,7 @@
         <v>412</v>
       </c>
       <c r="B402" t="n">
-        <v>-1.294054508209229</v>
+        <v>0.003763990011066198</v>
       </c>
     </row>
     <row r="403">
@@ -3653,7 +3653,7 @@
         <v>413</v>
       </c>
       <c r="B403" t="n">
-        <v>-1.282707571983337</v>
+        <v>0.003160289255902171</v>
       </c>
     </row>
     <row r="404">
@@ -3661,7 +3661,7 @@
         <v>414</v>
       </c>
       <c r="B404" t="n">
-        <v>-1.29079008102417</v>
+        <v>0.002449034713208675</v>
       </c>
     </row>
     <row r="405">
@@ -3669,7 +3669,7 @@
         <v>415</v>
       </c>
       <c r="B405" t="n">
-        <v>-1.287701845169067</v>
+        <v>0.002181005198508501</v>
       </c>
     </row>
     <row r="406">
@@ -3677,7 +3677,7 @@
         <v>416</v>
       </c>
       <c r="B406" t="n">
-        <v>-1.228124976158142</v>
+        <v>0.00215633143670857</v>
       </c>
     </row>
     <row r="407">
@@ -3685,7 +3685,7 @@
         <v>417</v>
       </c>
       <c r="B407" t="n">
-        <v>-1.159591197967529</v>
+        <v>0.001988742966204882</v>
       </c>
     </row>
     <row r="408">
@@ -3693,7 +3693,7 @@
         <v>418</v>
       </c>
       <c r="B408" t="n">
-        <v>-1.061507701873779</v>
+        <v>0.001826198189519346</v>
       </c>
     </row>
     <row r="409">
@@ -3701,7 +3701,7 @@
         <v>419</v>
       </c>
       <c r="B409" t="n">
-        <v>-0.9102296233177185</v>
+        <v>0.001907079247757792</v>
       </c>
     </row>
     <row r="410">
@@ -3709,7 +3709,7 @@
         <v>420</v>
       </c>
       <c r="B410" t="n">
-        <v>-0.7957665324211121</v>
+        <v>0.002959561999887228</v>
       </c>
     </row>
     <row r="411">
@@ -3717,7 +3717,7 @@
         <v>421</v>
       </c>
       <c r="B411" t="n">
-        <v>-0.7578716278076172</v>
+        <v>0.002935986733064055</v>
       </c>
     </row>
     <row r="412">
@@ -3725,7 +3725,7 @@
         <v>422</v>
       </c>
       <c r="B412" t="n">
-        <v>-0.7677428126335144</v>
+        <v>0.001693371450528502</v>
       </c>
     </row>
     <row r="413">
@@ -3733,7 +3733,7 @@
         <v>423</v>
       </c>
       <c r="B413" t="n">
-        <v>-0.8572929501533508</v>
+        <v>0.001156407292000949</v>
       </c>
     </row>
     <row r="414">
@@ -3741,7 +3741,7 @@
         <v>424</v>
       </c>
       <c r="B414" t="n">
-        <v>-0.8025443553924561</v>
+        <v>0.0009786509908735752</v>
       </c>
     </row>
     <row r="415">
@@ -3749,7 +3749,7 @@
         <v>425</v>
       </c>
       <c r="B415" t="n">
-        <v>-0.8354992270469666</v>
+        <v>0.000969528395216912</v>
       </c>
     </row>
     <row r="416">
@@ -3757,7 +3757,7 @@
         <v>426</v>
       </c>
       <c r="B416" t="n">
-        <v>-0.9005423188209534</v>
+        <v>0.0009315293864347041</v>
       </c>
     </row>
     <row r="417">
@@ -3765,7 +3765,7 @@
         <v>427</v>
       </c>
       <c r="B417" t="n">
-        <v>-0.9719409942626953</v>
+        <v>0.001000124611891806</v>
       </c>
     </row>
     <row r="418">
@@ -3773,7 +3773,7 @@
         <v>428</v>
       </c>
       <c r="B418" t="n">
-        <v>-1.037332773208618</v>
+        <v>0.0009640377829782665</v>
       </c>
     </row>
     <row r="419">
@@ -3781,7 +3781,7 @@
         <v>429</v>
       </c>
       <c r="B419" t="n">
-        <v>-1.075382828712463</v>
+        <v>0.0009996898006647825</v>
       </c>
     </row>
     <row r="420">
@@ -3789,7 +3789,7 @@
         <v>430</v>
       </c>
       <c r="B420" t="n">
-        <v>-1.078436613082886</v>
+        <v>0.001220647478476167</v>
       </c>
     </row>
     <row r="421">
@@ -3797,7 +3797,7 @@
         <v>431</v>
       </c>
       <c r="B421" t="n">
-        <v>-0.99326092004776</v>
+        <v>0.001823108061216772</v>
       </c>
     </row>
     <row r="422">
@@ -3805,7 +3805,7 @@
         <v>432</v>
       </c>
       <c r="B422" t="n">
-        <v>-0.918607234954834</v>
+        <v>0.002188252750784159</v>
       </c>
     </row>
     <row r="423">
@@ -3813,7 +3813,7 @@
         <v>433</v>
       </c>
       <c r="B423" t="n">
-        <v>-0.8698645234107971</v>
+        <v>0.001973522361367941</v>
       </c>
     </row>
     <row r="424">
@@ -3821,7 +3821,7 @@
         <v>434</v>
       </c>
       <c r="B424" t="n">
-        <v>-0.9061816334724426</v>
+        <v>0.001424594316631556</v>
       </c>
     </row>
     <row r="425">
@@ -3829,7 +3829,7 @@
         <v>435</v>
       </c>
       <c r="B425" t="n">
-        <v>-0.9086765050888062</v>
+        <v>0.00148235191591084</v>
       </c>
     </row>
     <row r="426">
@@ -3837,7 +3837,7 @@
         <v>436</v>
       </c>
       <c r="B426" t="n">
-        <v>-0.9640842080116272</v>
+        <v>0.001472381642088294</v>
       </c>
     </row>
     <row r="427">
@@ -3845,7 +3845,7 @@
         <v>437</v>
       </c>
       <c r="B427" t="n">
-        <v>-0.9212831258773804</v>
+        <v>0.001347011886537075</v>
       </c>
     </row>
     <row r="428">
@@ -3853,7 +3853,7 @@
         <v>438</v>
       </c>
       <c r="B428" t="n">
-        <v>-0.9242046475410461</v>
+        <v>0.001308019855059683</v>
       </c>
     </row>
     <row r="429">
@@ -3861,7 +3861,7 @@
         <v>439</v>
       </c>
       <c r="B429" t="n">
-        <v>-0.9692716002464294</v>
+        <v>0.001232375972904265</v>
       </c>
     </row>
     <row r="430">
@@ -3869,7 +3869,7 @@
         <v>440</v>
       </c>
       <c r="B430" t="n">
-        <v>-0.9761072993278503</v>
+        <v>0.001112482161261141</v>
       </c>
     </row>
     <row r="431">
@@ -3877,7 +3877,7 @@
         <v>441</v>
       </c>
       <c r="B431" t="n">
-        <v>-1.018924713134766</v>
+        <v>0.0009056765120476484</v>
       </c>
     </row>
     <row r="432">
@@ -3885,7 +3885,7 @@
         <v>442</v>
       </c>
       <c r="B432" t="n">
-        <v>-1.011701345443726</v>
+        <v>0.0008107734029181302</v>
       </c>
     </row>
     <row r="433">
@@ -3893,7 +3893,7 @@
         <v>443</v>
       </c>
       <c r="B433" t="n">
-        <v>-0.9781413674354553</v>
+        <v>0.0007876751478761435</v>
       </c>
     </row>
     <row r="434">
@@ -3901,7 +3901,7 @@
         <v>444</v>
       </c>
       <c r="B434" t="n">
-        <v>-0.9182554483413696</v>
+        <v>0.0006862618611194193</v>
       </c>
     </row>
     <row r="435">
@@ -3909,7 +3909,7 @@
         <v>445</v>
       </c>
       <c r="B435" t="n">
-        <v>-0.8630270957946777</v>
+        <v>0.000726626196410507</v>
       </c>
     </row>
     <row r="436">
@@ -3917,7 +3917,7 @@
         <v>446</v>
       </c>
       <c r="B436" t="n">
-        <v>-0.8613532185554504</v>
+        <v>0.0007061675423756242</v>
       </c>
     </row>
     <row r="437">
@@ -3925,7 +3925,7 @@
         <v>447</v>
       </c>
       <c r="B437" t="n">
-        <v>-0.9297359585762024</v>
+        <v>0.0008734179427847266</v>
       </c>
     </row>
     <row r="438">
@@ -3933,7 +3933,7 @@
         <v>448</v>
       </c>
       <c r="B438" t="n">
-        <v>-0.8874453902244568</v>
+        <v>0.001231876201927662</v>
       </c>
     </row>
     <row r="439">
@@ -3941,7 +3941,7 @@
         <v>449</v>
       </c>
       <c r="B439" t="n">
-        <v>-0.882762610912323</v>
+        <v>0.00161608075723052</v>
       </c>
     </row>
     <row r="440">
@@ -3949,7 +3949,7 @@
         <v>450</v>
       </c>
       <c r="B440" t="n">
-        <v>-0.88942950963974</v>
+        <v>0.001910968916490674</v>
       </c>
     </row>
     <row r="441">
@@ -3957,7 +3957,7 @@
         <v>451</v>
       </c>
       <c r="B441" t="n">
-        <v>-0.9303538203239441</v>
+        <v>0.002047364134341478</v>
       </c>
     </row>
     <row r="442">
@@ -3965,7 +3965,7 @@
         <v>452</v>
       </c>
       <c r="B442" t="n">
-        <v>-0.9844438433647156</v>
+        <v>0.002393793314695358</v>
       </c>
     </row>
     <row r="443">
@@ -3973,7 +3973,7 @@
         <v>453</v>
       </c>
       <c r="B443" t="n">
-        <v>-0.9848202466964722</v>
+        <v>0.002357496414333582</v>
       </c>
     </row>
     <row r="444">
@@ -3981,7 +3981,7 @@
         <v>454</v>
       </c>
       <c r="B444" t="n">
-        <v>-0.9587646722793579</v>
+        <v>0.002089796820655465</v>
       </c>
     </row>
     <row r="445">
@@ -3989,7 +3989,7 @@
         <v>455</v>
       </c>
       <c r="B445" t="n">
-        <v>-0.8726714253425598</v>
+        <v>0.002221849514171481</v>
       </c>
     </row>
     <row r="446">
@@ -3997,7 +3997,7 @@
         <v>456</v>
       </c>
       <c r="B446" t="n">
-        <v>-0.8405303359031677</v>
+        <v>0.002497493755072355</v>
       </c>
     </row>
     <row r="447">
@@ -4005,7 +4005,7 @@
         <v>457</v>
       </c>
       <c r="B447" t="n">
-        <v>-0.7244969010353088</v>
+        <v>0.002026999834924936</v>
       </c>
     </row>
     <row r="448">
@@ -4013,7 +4013,7 @@
         <v>458</v>
       </c>
       <c r="B448" t="n">
-        <v>-0.7049302458763123</v>
+        <v>0.001504015875980258</v>
       </c>
     </row>
     <row r="449">
@@ -4021,7 +4021,7 @@
         <v>459</v>
       </c>
       <c r="B449" t="n">
-        <v>-0.6541194319725037</v>
+        <v>0.001764635439030826</v>
       </c>
     </row>
     <row r="450">
@@ -4029,7 +4029,7 @@
         <v>460</v>
       </c>
       <c r="B450" t="n">
-        <v>-0.638093113899231</v>
+        <v>0.002093958435580134</v>
       </c>
     </row>
     <row r="451">
@@ -4037,7 +4037,7 @@
         <v>461</v>
       </c>
       <c r="B451" t="n">
-        <v>-0.5895012021064758</v>
+        <v>0.002436026697978377</v>
       </c>
     </row>
     <row r="452">
@@ -4045,7 +4045,7 @@
         <v>462</v>
       </c>
       <c r="B452" t="n">
-        <v>-0.5825278162956238</v>
+        <v>0.00258968211710453</v>
       </c>
     </row>
     <row r="453">
@@ -4053,7 +4053,7 @@
         <v>463</v>
       </c>
       <c r="B453" t="n">
-        <v>-0.6198019981384277</v>
+        <v>0.002247278578579426</v>
       </c>
     </row>
     <row r="454">
@@ -4061,7 +4061,7 @@
         <v>464</v>
       </c>
       <c r="B454" t="n">
-        <v>-0.6735237240791321</v>
+        <v>0.002229125937446952</v>
       </c>
     </row>
     <row r="455">
@@ -4069,7 +4069,7 @@
         <v>465</v>
       </c>
       <c r="B455" t="n">
-        <v>-0.7063484787940979</v>
+        <v>0.002219017362222075</v>
       </c>
     </row>
     <row r="456">
@@ -4077,7 +4077,7 @@
         <v>466</v>
       </c>
       <c r="B456" t="n">
-        <v>-0.6947280168533325</v>
+        <v>0.002189832041040063</v>
       </c>
     </row>
     <row r="457">
@@ -4085,7 +4085,7 @@
         <v>467</v>
       </c>
       <c r="B457" t="n">
-        <v>-0.7071123123168945</v>
+        <v>0.002263592323288321</v>
       </c>
     </row>
     <row r="458">
@@ -4093,7 +4093,7 @@
         <v>468</v>
       </c>
       <c r="B458" t="n">
-        <v>-0.7291158437728882</v>
+        <v>0.002635679207742214</v>
       </c>
     </row>
     <row r="459">
@@ -4101,7 +4101,7 @@
         <v>469</v>
       </c>
       <c r="B459" t="n">
-        <v>-0.7477899193763733</v>
+        <v>0.002261222107335925</v>
       </c>
     </row>
     <row r="460">
@@ -4109,7 +4109,7 @@
         <v>470</v>
       </c>
       <c r="B460" t="n">
-        <v>-0.855787992477417</v>
+        <v>0.001684216200374067</v>
       </c>
     </row>
     <row r="461">
@@ -4117,7 +4117,7 @@
         <v>471</v>
       </c>
       <c r="B461" t="n">
-        <v>-0.9446138739585876</v>
+        <v>0.001404596026986837</v>
       </c>
     </row>
     <row r="462">
@@ -4125,7 +4125,7 @@
         <v>472</v>
       </c>
       <c r="B462" t="n">
-        <v>-0.9729084372520447</v>
+        <v>0.001111656310968101</v>
       </c>
     </row>
     <row r="463">
@@ -4133,7 +4133,7 @@
         <v>473</v>
       </c>
       <c r="B463" t="n">
-        <v>-1.039828419685364</v>
+        <v>0.0009860341669991612</v>
       </c>
     </row>
     <row r="464">
@@ -4141,7 +4141,7 @@
         <v>474</v>
       </c>
       <c r="B464" t="n">
-        <v>-1.045432448387146</v>
+        <v>0.0009163600043393672</v>
       </c>
     </row>
     <row r="465">
@@ -4149,7 +4149,7 @@
         <v>475</v>
       </c>
       <c r="B465" t="n">
-        <v>-1.133253693580627</v>
+        <v>0.0009656326728872955</v>
       </c>
     </row>
     <row r="466">
@@ -4157,7 +4157,7 @@
         <v>476</v>
       </c>
       <c r="B466" t="n">
-        <v>-1.174346804618835</v>
+        <v>0.0009113637497648597</v>
       </c>
     </row>
     <row r="467">
@@ -4165,7 +4165,7 @@
         <v>477</v>
       </c>
       <c r="B467" t="n">
-        <v>-1.226525783538818</v>
+        <v>0.0008621476008556783</v>
       </c>
     </row>
     <row r="468">
@@ -4173,7 +4173,7 @@
         <v>478</v>
       </c>
       <c r="B468" t="n">
-        <v>-1.229135036468506</v>
+        <v>0.0008934634970501065</v>
       </c>
     </row>
     <row r="469">
@@ -4181,7 +4181,7 @@
         <v>479</v>
       </c>
       <c r="B469" t="n">
-        <v>-1.185852885246277</v>
+        <v>0.0009614775772206485</v>
       </c>
     </row>
     <row r="470">
@@ -4189,7 +4189,7 @@
         <v>480</v>
       </c>
       <c r="B470" t="n">
-        <v>-1.14717173576355</v>
+        <v>0.001122921472415328</v>
       </c>
     </row>
     <row r="471">
@@ -4197,7 +4197,7 @@
         <v>481</v>
       </c>
       <c r="B471" t="n">
-        <v>-1.089861392974854</v>
+        <v>0.001085756462998688</v>
       </c>
     </row>
     <row r="472">
@@ -4205,7 +4205,7 @@
         <v>482</v>
       </c>
       <c r="B472" t="n">
-        <v>-1.153302907943726</v>
+        <v>0.001218917430378497</v>
       </c>
     </row>
     <row r="473">
@@ -4213,7 +4213,7 @@
         <v>483</v>
       </c>
       <c r="B473" t="n">
-        <v>-1.136813163757324</v>
+        <v>0.001518294680863619</v>
       </c>
     </row>
     <row r="474">
@@ -4221,7 +4221,7 @@
         <v>484</v>
       </c>
       <c r="B474" t="n">
-        <v>-1.173887729644775</v>
+        <v>0.001692871679551899</v>
       </c>
     </row>
     <row r="475">
@@ -4229,7 +4229,7 @@
         <v>485</v>
       </c>
       <c r="B475" t="n">
-        <v>-1.172261953353882</v>
+        <v>0.001909535960294306</v>
       </c>
     </row>
     <row r="476">
@@ -4237,7 +4237,7 @@
         <v>486</v>
       </c>
       <c r="B476" t="n">
-        <v>-1.188427448272705</v>
+        <v>0.001702579320408404</v>
       </c>
     </row>
     <row r="477">
@@ -4245,7 +4245,7 @@
         <v>487</v>
       </c>
       <c r="B477" t="n">
-        <v>-1.189626812934875</v>
+        <v>0.001603464246727526</v>
       </c>
     </row>
     <row r="478">
@@ -4253,7 +4253,7 @@
         <v>488</v>
       </c>
       <c r="B478" t="n">
-        <v>-1.174824237823486</v>
+        <v>0.001546191400848329</v>
       </c>
     </row>
     <row r="479">
@@ -4261,7 +4261,7 @@
         <v>489</v>
       </c>
       <c r="B479" t="n">
-        <v>-1.191725254058838</v>
+        <v>0.001429810537956655</v>
       </c>
     </row>
     <row r="480">
@@ -4269,7 +4269,7 @@
         <v>490</v>
       </c>
       <c r="B480" t="n">
-        <v>-1.189818382263184</v>
+        <v>0.001484285574406385</v>
       </c>
     </row>
     <row r="481">
@@ -4277,7 +4277,7 @@
         <v>491</v>
       </c>
       <c r="B481" t="n">
-        <v>-1.178602814674377</v>
+        <v>0.001662349095568061</v>
       </c>
     </row>
     <row r="482">
@@ -4285,7 +4285,7 @@
         <v>492</v>
       </c>
       <c r="B482" t="n">
-        <v>-1.134895086288452</v>
+        <v>0.001470805145800114</v>
       </c>
     </row>
     <row r="483">
@@ -4293,7 +4293,7 @@
         <v>493</v>
       </c>
       <c r="B483" t="n">
-        <v>-1.093517303466797</v>
+        <v>0.001333995955064893</v>
       </c>
     </row>
     <row r="484">
@@ -4301,7 +4301,7 @@
         <v>494</v>
       </c>
       <c r="B484" t="n">
-        <v>-1.046035528182983</v>
+        <v>0.001030722633004189</v>
       </c>
     </row>
     <row r="485">
@@ -4309,7 +4309,7 @@
         <v>495</v>
       </c>
       <c r="B485" t="n">
-        <v>-1.107557058334351</v>
+        <v>0.0009347145678475499</v>
       </c>
     </row>
     <row r="486">
@@ -4317,7 +4317,7 @@
         <v>496</v>
       </c>
       <c r="B486" t="n">
-        <v>-1.051234722137451</v>
+        <v>0.0009029794600792229</v>
       </c>
     </row>
     <row r="487">
@@ -4325,7 +4325,7 @@
         <v>497</v>
       </c>
       <c r="B487" t="n">
-        <v>-0.9768152832984924</v>
+        <v>0.0008077974780462682</v>
       </c>
     </row>
     <row r="488">
@@ -4333,7 +4333,7 @@
         <v>498</v>
       </c>
       <c r="B488" t="n">
-        <v>-0.9310917854309082</v>
+        <v>0.0008119354606606066</v>
       </c>
     </row>
     <row r="489">
@@ -4341,7 +4341,7 @@
         <v>499</v>
       </c>
       <c r="B489" t="n">
-        <v>-0.9399601221084595</v>
+        <v>0.0008604668546468019</v>
       </c>
     </row>
     <row r="490">
@@ -4349,7 +4349,7 @@
         <v>500</v>
       </c>
       <c r="B490" t="n">
-        <v>-0.9414135813713074</v>
+        <v>0.0007601169054396451</v>
       </c>
     </row>
     <row r="491">
@@ -4357,7 +4357,7 @@
         <v>501</v>
       </c>
       <c r="B491" t="n">
-        <v>-0.9753101468086243</v>
+        <v>0.0007517628255300224</v>
       </c>
     </row>
     <row r="492">
@@ -4365,7 +4365,7 @@
         <v>502</v>
       </c>
       <c r="B492" t="n">
-        <v>-0.9681340456008911</v>
+        <v>0.0008289016550406814</v>
       </c>
     </row>
     <row r="493">
@@ -4373,7 +4373,7 @@
         <v>503</v>
       </c>
       <c r="B493" t="n">
-        <v>-0.9304704070091248</v>
+        <v>0.001493423711508512</v>
       </c>
     </row>
     <row r="494">
@@ -4381,7 +4381,7 @@
         <v>504</v>
       </c>
       <c r="B494" t="n">
-        <v>-0.9236279129981995</v>
+        <v>0.00288912863470614</v>
       </c>
     </row>
     <row r="495">
@@ -4389,7 +4389,7 @@
         <v>505</v>
       </c>
       <c r="B495" t="n">
-        <v>-0.8064479827880859</v>
+        <v>0.003502644132822752</v>
       </c>
     </row>
     <row r="496">
@@ -4397,7 +4397,7 @@
         <v>506</v>
       </c>
       <c r="B496" t="n">
-        <v>-0.9098721146583557</v>
+        <v>0.00366296386346221</v>
       </c>
     </row>
     <row r="497">
@@ -4405,7 +4405,7 @@
         <v>507</v>
       </c>
       <c r="B497" t="n">
-        <v>-0.9234842658042908</v>
+        <v>0.004205606877803802</v>
       </c>
     </row>
     <row r="498">
@@ -4413,7 +4413,7 @@
         <v>508</v>
       </c>
       <c r="B498" t="n">
-        <v>-0.9340554475784302</v>
+        <v>0.004508035257458687</v>
       </c>
     </row>
     <row r="499">
@@ -4421,7 +4421,7 @@
         <v>509</v>
       </c>
       <c r="B499" t="n">
-        <v>-1.009343385696411</v>
+        <v>0.004848643206059933</v>
       </c>
     </row>
     <row r="500">
@@ -4429,7 +4429,7 @@
         <v>510</v>
       </c>
       <c r="B500" t="n">
-        <v>-1.010895490646362</v>
+        <v>0.003767753951251507</v>
       </c>
     </row>
     <row r="501">
@@ -4437,7 +4437,7 @@
         <v>511</v>
       </c>
       <c r="B501" t="n">
-        <v>-0.9910502433776855</v>
+        <v>0.003200308885425329</v>
       </c>
     </row>
     <row r="502">
@@ -4445,7 +4445,7 @@
         <v>512</v>
       </c>
       <c r="B502" t="n">
-        <v>-0.9663257002830505</v>
+        <v>0.002655615331605077</v>
       </c>
     </row>
     <row r="503">
@@ -4453,7 +4453,7 @@
         <v>513</v>
       </c>
       <c r="B503" t="n">
-        <v>-0.9198841452598572</v>
+        <v>0.00268360273912549</v>
       </c>
     </row>
     <row r="504">
@@ -4461,7 +4461,7 @@
         <v>514</v>
       </c>
       <c r="B504" t="n">
-        <v>-0.7653370499610901</v>
+        <v>0.002688124077394605</v>
       </c>
     </row>
     <row r="505">
@@ -4469,7 +4469,7 @@
         <v>515</v>
       </c>
       <c r="B505" t="n">
-        <v>-0.5947330594062805</v>
+        <v>0.003397563006728888</v>
       </c>
     </row>
     <row r="506">
@@ -4477,7 +4477,7 @@
         <v>516</v>
       </c>
       <c r="B506" t="n">
-        <v>-0.4385236501693726</v>
+        <v>0.005534468684345484</v>
       </c>
     </row>
     <row r="507">
@@ -4485,7 +4485,7 @@
         <v>517</v>
       </c>
       <c r="B507" t="n">
-        <v>-0.3920544385910034</v>
+        <v>0.008591162972152233</v>
       </c>
     </row>
     <row r="508">
@@ -4493,7 +4493,7 @@
         <v>518</v>
       </c>
       <c r="B508" t="n">
-        <v>-0.3317428529262543</v>
+        <v>0.007742600049823523</v>
       </c>
     </row>
     <row r="509">
@@ -4501,7 +4501,7 @@
         <v>519</v>
       </c>
       <c r="B509" t="n">
-        <v>-0.2589451372623444</v>
+        <v>0.006753505207598209</v>
       </c>
     </row>
     <row r="510">
@@ -4509,7 +4509,7 @@
         <v>520</v>
       </c>
       <c r="B510" t="n">
-        <v>-0.1163449510931969</v>
+        <v>0.009929908439517021</v>
       </c>
     </row>
     <row r="511">
@@ -4517,7 +4517,7 @@
         <v>521</v>
       </c>
       <c r="B511" t="n">
-        <v>0.06935881823301315</v>
+        <v>0.01738779246807098</v>
       </c>
     </row>
     <row r="512">
@@ -4525,7 +4525,7 @@
         <v>522</v>
       </c>
       <c r="B512" t="n">
-        <v>0.2345442622900009</v>
+        <v>0.03633065521717072</v>
       </c>
     </row>
     <row r="513">
@@ -4533,7 +4533,7 @@
         <v>523</v>
       </c>
       <c r="B513" t="n">
-        <v>0.218868762254715</v>
+        <v>0.05836999043822289</v>
       </c>
     </row>
     <row r="514">
@@ -4541,7 +4541,7 @@
         <v>524</v>
       </c>
       <c r="B514" t="n">
-        <v>0.1286084204912186</v>
+        <v>0.09025833755731583</v>
       </c>
     </row>
     <row r="515">
@@ -4549,7 +4549,7 @@
         <v>525</v>
       </c>
       <c r="B515" t="n">
-        <v>0.02759488858282566</v>
+        <v>0.1701098680496216</v>
       </c>
     </row>
     <row r="516">
@@ -4557,7 +4557,7 @@
         <v>526</v>
       </c>
       <c r="B516" t="n">
-        <v>-0.09013297408819199</v>
+        <v>0.2530735433101654</v>
       </c>
     </row>
     <row r="517">
@@ -4565,7 +4565,7 @@
         <v>527</v>
       </c>
       <c r="B517" t="n">
-        <v>-0.1260789185762405</v>
+        <v>0.4121103882789612</v>
       </c>
     </row>
     <row r="518">
@@ -4573,7 +4573,7 @@
         <v>528</v>
       </c>
       <c r="B518" t="n">
-        <v>-0.3452223241329193</v>
+        <v>0.4091049134731293</v>
       </c>
     </row>
   </sheetData>
